--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,18 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,40 +143,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,17 +763,17 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="F4" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>9.6</v>
+      <c r="F4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>17</v>
@@ -821,48 +782,52 @@
         <v>6.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="n">
+        <v>16.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>84</v>
+        <v>845</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>227.8</v>
+      <c r="Q4" s="3" t="n">
+        <v>117.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>651.3</v>
+      <c r="S4" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>56.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>13.6</v>
@@ -881,17 +846,17 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>10.8</v>
+      <c r="G5" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -903,52 +868,52 @@
         <v>9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>823.5</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>28.4</v>
+        <v>3.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>21.8</v>
+      <c r="S5" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U5" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -964,23 +929,23 @@
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.6</v>
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>12.6</v>
@@ -988,9 +953,11 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="M6" s="3" t="n">
-        <v>162.4</v>
+        <v>1.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
@@ -999,10 +966,10 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>481.1</v>
+        <v>47.1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>21.8</v>
@@ -1014,18 +981,20 @@
         <v>56.4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n">
+        <v>57.8</v>
+      </c>
       <c r="Z6" s="3" t="n">
         <v>14</v>
       </c>
@@ -1043,64 +1012,66 @@
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>109.2</v>
+      <c r="K7" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54621561
+81
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>28341.2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>42.6</v>
+        <v>4.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="W7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1126,40 +1097,42 @@
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="13" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>23.7</v>
+      <c r="D8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="J8" s="3" t="n">
-        <v>19.2</v>
+        <v>1.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>18.6</v>
       </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
@@ -1168,15 +1141,19 @@
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V8" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.7</v>
@@ -1185,7 +1162,7 @@
         <v>56.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1194.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1201,41 +1178,46 @@
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="13" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>117</v>
+      <c r="D9" s="10" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>134.6</v>
+        <v>34.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>18.5</v>
+        <v>84.7</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
@@ -1244,31 +1226,31 @@
         <v>145.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10.6</v>
+        <v>196.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>12.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>288.1</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>2938.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>73.5</v>
+        <v>13.4</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>970.1</v>
+        <v>914.4</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1.4</v>
+        <v>194.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1284,32 +1266,32 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="13" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E10" s="13" t="n">
+      <c r="D10" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>11.5</v>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.5</v>
+        <v>46.4</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>21.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1318,10 +1300,10 @@
         <v>18</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>84.7</v>
+        <v>820.1</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1330,28 +1312,28 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>0.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>4.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.4</v>
+        <v>1.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1367,70 +1349,74 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="13" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="H11" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>18</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.1</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>44.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.8</v>
+        <v>48.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>900.6</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>18.4</v>
+        <v>700.6</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
+        <v>5.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>20.2</v>
+        <v>1.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>600.1</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1446,46 +1432,46 @@
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="11" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>16.4</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>49.9</v>
+        <v>14.6</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>23.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q12" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1495,7 +1481,7 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>16.2</v>
@@ -1504,13 +1490,13 @@
         <v>25.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>600.1</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>13</v>
@@ -1529,69 +1515,71 @@
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G13" s="13" t="n">
+      <c r="D13" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L13" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="M13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>83.5</v>
+        <v>24.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>66</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.9</v>
+        <v>1.9</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>58</v>
+        <v>5.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>17.4</v>
+      <c r="W13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>10.6</v>
@@ -1610,71 +1598,71 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="13" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E14" s="13" t="n">
+      <c r="D14" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G14" s="13" t="n">
+      <c r="F14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>19</v>
+        <v>10.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>213.4</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>26.8</v>
+        <v>46.2</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>118.2</v>
+      <c r="S14" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>21.5</v>
+        <v>52.1</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>17</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>23.6</v>
+        <v>50.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>1.9</v>
+      <c r="X14" s="8" t="n">
+        <v>39.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61.8</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1693,32 +1681,36 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="13" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>11</v>
+      <c r="D15" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>64.59999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>220.5</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1730,22 +1722,22 @@
         <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>72.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>21.2</v>
+      <c r="R15" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>22.1</v>
+        <v>111.9</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
@@ -1757,10 +1749,10 @@
         <v>17.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1776,20 +1768,20 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="13" t="n">
-        <v>139</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>89</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>114</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>25</v>
+      <c r="D16" s="10" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>20.6</v>
@@ -1798,52 +1790,52 @@
         <v>50.6</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>220.3</v>
+        <v>18.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>84</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>72.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>138.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>102.1</v>
+        <v>132.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>28.8</v>
+        <v>988.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>211.9</v>
+        <v>53.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>814.4</v>
+        <v>813.4</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>122.8</v>
+        <v>12.8</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>933.5</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>55</v>
+        <v>202.5</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1859,29 +1851,33 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>10</v>
+      <c r="G17" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>6.1</v>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+61
+</t>
+        </is>
       </c>
       <c r="J17" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>18.6</v>
@@ -1889,42 +1885,44 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>284.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>53.2</v>
+        <v>482.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1940,74 +1938,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="15" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="E18" s="15" t="n">
+      <c r="D18" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>13.6</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>18.6</v>
+        <v>43.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.6</v>
+        <v>164.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>12.1</v>
+        <v>118.2</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>504.1</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>41.5</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>24.8</v>
+        <v>0.1</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>432.1</v>
+        <v>46.8</v>
       </c>
       <c r="U18" s="3" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>864.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="X18" s="3" t="n">
-        <v>10.1</v>
+        <v>109.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>580.1</v>
+        <v>8</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2023,72 +2021,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="13" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>17.6</v>
+      <c r="D19" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0.4</v>
+        <v>13.5</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>209.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>4.5</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2104,41 +2102,41 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>10.6</v>
+      <c r="D20" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.1</v>
+        <v>12.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>11.9</v>
+        <v>8.6</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>881</v>
+        <v>80.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2150,28 +2148,28 @@
         <v>21.8</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>148.5</v>
+        <v>56</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>26.4</v>
+        <v>465.4</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>50.5</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2187,62 +2185,62 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E21" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>26.5</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.8</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>15.9</v>
+        <v>68.3</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.6</v>
@@ -2251,7 +2249,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2270,74 +2268,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="13" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>17</v>
+      <c r="D22" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.6</v>
+        <v>4.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>18.8</v>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>23</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>68.3</v>
+        <v>267.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v>19.6</v>
+        <v>39</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>16.8</v>
+        <v>25.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>726.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>25.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2353,74 +2351,72 @@
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="10" t="n">
         <v>145.6</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="10" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="F23" s="20" t="n">
-        <v>110.8</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>56.8</v>
+      <c r="F23" s="10" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>84.8</v>
+        <v>34.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.2</v>
+        <v>32.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>5.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93</v>
+        <v>1.6</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>357.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>126.8</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>740.8</v>
+        <v>740.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.9</v>
+        <v>113.4</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>111.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96.7</v>
+        <v>68.3</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>975.1</v>
+        <v>175.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>95.59999999999999</v>
-      </c>
+        <v>1238.5</v>
+      </c>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>30.5</v>
+        <v>3152.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>52.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2436,74 +2432,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="20" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E24" s="20" t="n">
+      <c r="D24" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="20" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>11.2</v>
+      <c r="F24" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>52.9</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6.8</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>28.1</v>
+        <v>0.8</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>20.7</v>
+        <v>0.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>3.5</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>24.7</v>
+        <v>4.7</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>19.1</v>
+        <v>3.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.8</v>
+        <v>121.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2519,21 +2515,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="15" t="n">
+      <c r="D25" s="9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E25" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>18.8</v>
+      <c r="F25" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>26.1</v>
+        <v>16.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
@@ -2542,46 +2540,46 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>47.1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>83.5</v>
+        <v>356.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>34.1</v>
+        <v>54.1</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>19.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>605.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0.2</v>
+        <v>138.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>13.9</v>
+        <v>438.1</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>8.9</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2600,44 +2598,44 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="13" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E26" s="13" t="n">
+      <c r="D26" s="9" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>11.6</v>
+      <c r="F26" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16</v>
+        <v>11.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>304.1</v>
+        <v>0.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>16.8</v>
+      <c r="M26" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2646,7 +2644,7 @@
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>52.2</v>
@@ -2654,20 +2652,20 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>24.4</v>
+      <c r="V26" s="8" t="n">
+        <v>4494.4</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2683,43 +2681,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>21.4</v>
-      </c>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>465.4</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>27.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2730,7 +2732,7 @@
       <c r="T27" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2740,7 +2742,7 @@
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>64</v>
@@ -2762,72 +2764,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="13" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G28" s="13" t="n">
+      <c r="D28" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>60.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O28" s="3" t="n"/>
+      <c r="M28" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
+        <v>22.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>20.7</v>
+        <v>0.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>56.1</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59</v>
+        <v>52.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2843,14 +2847,14 @@
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" s="13" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>22.4</v>
+      <c r="E29" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>9.4</v>
@@ -2859,22 +2863,22 @@
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.4</v>
+        <v>424.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.9</v>
+        <v>12.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>89</v>
@@ -2892,22 +2896,22 @@
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.2</v>
+        <v>5.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>229.6</v>
+      <c r="V29" s="3" t="n">
+        <v>43.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>66.2</v>
+        <v>6.2</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2926,72 +2930,74 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="20" t="n">
-        <v>133.4</v>
-      </c>
-      <c r="E30" s="20" t="n">
+      <c r="D30" s="10" t="n">
+        <v>1353.2</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="20" t="n">
-        <v>22.1</v>
+      <c r="F30" s="10" t="n">
+        <v>2.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9.1</v>
+        <v>41.7</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2.8</v>
+        <v>89</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>115.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>139</v>
+        <v>139.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>102.4</v>
+        <v>19.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>298</v>
+        <v>5.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="V30" s="3" t="n"/>
+        <v>28.1</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>95</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>5.6</v>
+        <v>34.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>45.1</v>
+        <v>4981.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3007,72 +3013,72 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="20" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E31" s="20" t="n">
+      <c r="D31" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="20" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="F31" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H31" s="8" t="n">
-        <v>10.6</v>
+      <c r="H31" s="3" t="n">
+        <v>876.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>944.1</v>
+        <v>94</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>23.6</v>
+        <v>43.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>19.8</v>
+        <v>8.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>67.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3088,62 +3094,62 @@
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>26.7</v>
+        <v>1.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>482.4</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>28.5</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
+        <v>6.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
@@ -3152,7 +3158,7 @@
         <v>19.5</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>71</v>
+        <v>21.8</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>8</v>
@@ -3171,29 +3177,29 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E33" s="13" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G33" s="13" t="n">
+      <c r="E33" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.4</v>
@@ -3202,41 +3208,43 @@
         <v>565.1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.8</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q33" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V33" s="3" t="n"/>
+      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>75</v>
+        <v>16.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3252,56 +3260,56 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="G34" s="13" t="n">
-        <v>10.2</v>
+      <c r="G34" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>57.2</v>
+        <v>57.6</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>15.3</v>
@@ -3310,16 +3318,16 @@
         <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3335,72 +3343,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E35" s="13" t="n">
+      <c r="D35" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G35" s="13" t="n">
+      <c r="F35" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>17</v>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="N35" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>900.6</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>24.2</v>
+        <v>4.2</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>20.4</v>
+        <v>6.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>20.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>86.5</v>
+        <v>6</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>3.2</v>
+        <v>32.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3416,61 +3426,63 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="13" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E36" s="13" t="n">
+      <c r="D36" s="9" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F36" s="13" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>10.8</v>
+      <c r="F36" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N36" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>83.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.8</v>
+        <v>61.8</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3478,10 +3490,10 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.2</v>
+        <v>35.2</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3497,26 +3509,26 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="13" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="E37" s="13" t="n">
+      <c r="D37" s="10" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>88.2</v>
       </c>
-      <c r="F37" s="13" t="n">
-        <v>111</v>
-      </c>
-      <c r="G37" s="3" t="n">
+      <c r="F37" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G37" s="9" t="n">
         <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.9</v>
+        <v>20.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.2</v>
+        <v>3.1</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>18.6</v>
@@ -3525,41 +3537,43 @@
         <v>18.6</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>846.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>595.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1139.5</v>
+        <v>87</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>131.8</v>
+        <v>134.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>102.2</v>
+        <v>1922.8</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="T37" s="3" t="n"/>
+        <v>7.7</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>56.4</v>
+      </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>709.6</v>
+        <v>713.6</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>101.6</v>
+        <v>18.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>386.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>7.9</v>
+        <v>86.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3578,71 +3592,83 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="13" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="D38" s="10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>895</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>20.9</v>
+      <c r="H38" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+9
+</t>
+        </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.7</v>
+        <v>27.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>737.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.8</v>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+248
+</t>
+        </is>
       </c>
       <c r="R38" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>0.6</v>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+203
+</t>
+        </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.7</v>
+        <v>57.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>14.9</v>
+        <v>4.7</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.9</v>
+        <v>0.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.2</v>
@@ -3661,20 +3687,20 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F39" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+      <c r="G39" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.2</v>
@@ -3683,52 +3709,52 @@
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>9.6</v>
+        <v>27.3</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="M39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>2208.4</v>
-      </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>114.9</v>
+        <v>1.9</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>39.4</v>
+        <v>35.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>28.5</v>
+        <v>19.6</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>181.1</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3744,74 +3770,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n"/>
-      <c r="D40" s="13" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F40" s="13" t="n">
+      <c r="D40" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <v>71.8</v>
+      <c r="G40" s="11" t="n">
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>194.1</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>126.2</v>
+        <v>84</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>6.6</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>56.8</v>
+        <v>5.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>28.8</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.5</v>
+        <v>14.4</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3827,70 +3853,72 @@
         </is>
       </c>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D41" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F41" s="14" t="n"/>
+      <c r="F41" s="11" t="n">
+        <v>21.3</v>
+      </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>59.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>17.2</v>
+      <c r="M41" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>81</v>
+        <v>840.1</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>57.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>19.6</v>
+        <v>14.4</v>
       </c>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="3" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>19.6</v>
+        <v>76.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3906,47 +3934,47 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>14</v>
+      <c r="E42" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.4</v>
+        <v>23.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13</v>
+        <v>24.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28.6</v>
+        <v>0.3</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
@@ -3955,22 +3983,26 @@
         <v>20.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="W42" s="3" t="n">
-        <v>20</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3988,70 +4020,72 @@
       <c r="D43" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E43" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
+      <c r="E43" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J43" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>4.9</v>
+        <v>28.6</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>0.6</v>
+        <v>30.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.9</v>
+        <v>2.9</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>26.4</v>
+        <v>6.9</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>427</v>
+      <c r="X43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4066,63 +4100,69 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
+      <c r="I44" s="8" t="n">
+        <v>125.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.3</v>
+        <v>1.3</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>765</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>21.8</v>
+        <v>766.1</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>157.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>20.9</v>
+        <v>62.6</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="V44" s="8" t="n">
-        <v>14.8</v>
+      <c r="V44" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X44" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -4141,75 +4181,77 @@
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
-      <c r="D45" s="20" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>22.5</v>
+      <c r="D45" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>2.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>32.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.9</v>
+        <v>61.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>499.6</v>
+        <v>139.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>998.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>52.6</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>165</v>
+        <v>21.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>765</v>
+        <v>27.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>111.1</v>
+        <v>26.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>1.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>107.1</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>143.9</v>
+        <v>23.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>114.8</v>
+        <v>1.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>19.1</v>
+        <v>4</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>10.4</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4224,17 +4266,21 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="20" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>10.8</v>
+      <c r="D46" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4245,51 +4291,62 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>7.8</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>20.1</v>
+        <v>157.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>917.9</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2919292795
+24
+12
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>19.1</v>
+        <v>1.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>10.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,20 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -165,9 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -780,37 +771,61 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
+      <c r="C4" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>9.6</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="H4" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="n">
+        <v>513.9</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -830,32 +845,56 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
+      <c r="D5" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="P5" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -863,7 +902,7 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -889,44 +928,62 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
+      <c r="D6" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="8" t="n">
+      <c r="F6" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>7.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T6" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>20</v>
@@ -954,50 +1011,72 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="9" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="D7" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H7" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>484.1</v>
+      </c>
       <c r="N7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.5</v>
+      </c>
       <c r="T7" s="3" t="n">
-        <v>146.4</v>
+        <v>142.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1014,47 +1093,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S8" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>24.2</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>25.8</v>
+      </c>
       <c r="W8" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
@@ -1074,68 +1167,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="D9" s="10" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>115.2</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>824.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>565.4</v>
+        <v>26.6</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.1</v>
+        <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>82.2</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.8</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>122.9</v>
+        <v>42.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1943.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1096</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>19.7</v>
+        <v>100.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>201.1</v>
+        <v>2099.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.2</v>
+        <v>992.6</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>911.4</v>
+        <v>11.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0.4</v>
+        <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>14.4</v>
+        <v>615</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1151,70 +1250,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>27.1</v>
+      <c r="D10" s="10" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>824.4</v>
+        <v>16.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>34.1</v>
+        <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>565.4</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>34.1</v>
+        <v>18</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>122.9</v>
+        <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>943.8</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>102.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>163.1</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>29461</v>
+        <v>51</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>12.2</v>
+        <v>25.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="X10" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y10" s="3" t="n">
-        <v>0.4</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>165</v>
+        <v>13.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1230,57 +1333,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="D11" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H11" s="3" t="n">
-        <v>16.8</v>
+        <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>16.9</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O11" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
+        <v>890.9</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q11" s="8" t="n">
-        <v>29.2</v>
+        <v>18.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
-        <v>19.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1294,65 +1403,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="8" t="n">
+      <c r="C12" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>182</v>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q12" s="3" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>18.4</v>
+        <v>21.6</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>19.1</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>28.9</v>
+        <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1367,59 +1486,77 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="8" t="n">
-        <v>11.6</v>
+      <c r="C13" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>41.2</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>182</v>
+        <v>9.6</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+        <v>283.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>41.4</v>
+      </c>
       <c r="Q13" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18.4</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U13" s="3" t="inlineStr"/>
+        <v>51.1</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V13" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W13" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="Z13" s="3" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1435,58 +1572,74 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="D14" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>16.4</v>
+        <v>27.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>191.6</v>
+        <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>24.9</v>
+        <v>74.5</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>51.1</v>
+        <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>14</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X14" s="3" t="n">
-        <v>19.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>13.8</v>
+        <v>10.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1502,52 +1655,72 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="D15" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="I15" s="3" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R15" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>58</v>
+        <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.6</v>
+        <v>114.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1563,46 +1736,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="9" t="n">
-        <v>119.1</v>
+      <c r="D16" s="12" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>900.6</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>980.8</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>2281.2</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>104.1</v>
+      </c>
       <c r="S16" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>86.2</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
+        <v>152.8</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>94.5</v>
+      </c>
       <c r="X16" s="3" t="n">
-        <v>187.8</v>
+        <v>92.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>25</v>
+        <v>304.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>114.6</v>
+        <v>14.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1617,69 +1818,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="9" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>134.4</v>
+      <c r="C17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>49.8</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>10.6</v>
+        <v>16.8</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>98.8</v>
+        <v>13.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>266.2</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="8" t="n">
-        <v>22.8</v>
+        <v>52.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>99.3</v>
+        <v>12</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>302</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>61</v>
+        <v>12.2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1694,54 +1901,74 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="13" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E18" s="13" t="n">
+      <c r="C18" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F18" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>26.8</v>
+      <c r="F18" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>14.6</v>
+      </c>
       <c r="Q18" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V18" s="3" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>12.2</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1756,48 +1983,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.5</v>
+      <c r="D19" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T19" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="n">
-        <v>2948.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.1</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="Z19" s="3" t="n">
-        <v>1149.5</v>
+        <v>19.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1813,40 +2064,72 @@
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="D20" s="12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>23.8</v>
+      </c>
       <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T20" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
+        <v>48.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -1862,38 +2145,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
+      <c r="D21" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>12.6</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>948.5</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="3" t="inlineStr"/>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="inlineStr"/>
-      <c r="Z21" s="3" t="n">
-        <v>114.9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -1909,42 +2226,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="D22" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T22" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr"/>
+        <v>68.3</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="V22" s="3" t="n">
-        <v>24.4</v>
+        <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
-        <v>39</v>
+        <v>16.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>12.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1959,51 +2306,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>117.5</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>10.8</v>
+        <v>26.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>84.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="J23" s="3" t="n">
-        <v>1.4</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
+        <v>926.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>140.4</v>
+      </c>
       <c r="R23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>103.4</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>1180.4</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr"/>
+        <v>267.9</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
       <c r="V23" s="3" t="n">
-        <v>19.6</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>41.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>16</v>
+        <v>2216.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>5.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2018,71 +2391,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="9" t="n">
-        <v>945.6</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>26.6</v>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>31.1</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>156.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>80.40000000000001</v>
+        <v>28.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1267.8</v>
+        <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W24" s="8" t="n">
-        <v>20.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>94.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>52.8</v>
+        <v>12.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2097,58 +2474,70 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>19.6</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L25" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>28.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>221.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.7</v>
+        <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
-      <c r="W25" s="3" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2162,46 +2551,78 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>10.2</v>
+      </c>
       <c r="H26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="Q26" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
+        <v>28.8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S26" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>13.8</v>
+        <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="V26" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>29.4</v>
+      </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>112.8</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2215,46 +2636,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R27" s="3" t="inlineStr"/>
+      <c r="N27" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
+        <v>56.9</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y27" s="3" t="inlineStr"/>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2271,37 +2716,69 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
+      <c r="D28" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>19.8</v>
+      </c>
       <c r="G28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="3" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>5294</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>56.7</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y28" s="3" t="inlineStr"/>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2318,37 +2795,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="8" t="n">
-        <v>16.6</v>
+      <c r="D29" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q29" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
+        <v>25.6</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>659.5</v>
+      </c>
       <c r="U29" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2363,52 +2878,74 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="D30" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>131</v>
+      </c>
       <c r="I30" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr"/>
+        <v>2016.1</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2681.4</v>
+      </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.6</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>17.4</v>
+        <v>836.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
+        <v>420</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>125.6</v>
+        <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>19.8</v>
+        <v>1082</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T30" s="3" t="inlineStr"/>
+        <v>102.2</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>298.9</v>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>1818.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
-      <c r="Y30" s="3" t="inlineStr"/>
+        <v>985.6</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>316.2</v>
+      </c>
       <c r="Z30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2423,59 +2960,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="9" t="n">
-        <v>309.8</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="8" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>810</v>
+      <c r="C31" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>6.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>318.3</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr"/>
+        <v>16.7</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>59.8</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>30.4</v>
+        <v>19.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>1.5</v>
+        <v>23.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="X31" s="3" t="inlineStr"/>
-      <c r="Y31" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>69.2</v>
+      </c>
       <c r="Z31" s="3" t="n">
-        <v>249.8</v>
+        <v>10</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2490,54 +3043,76 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>26.8</v>
+        <v>15.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="X32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2551,62 +3126,74 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>16.9</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>2.7</v>
+        <v>28.6</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -2623,39 +3210,69 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="D34" s="9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>17.4</v>
+        <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R34" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>284.6</v>
+      </c>
       <c r="W34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -2671,41 +3288,71 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="8" t="n">
-        <v>17.2</v>
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N35" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X35" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="inlineStr"/>
@@ -2722,35 +3369,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>26.4</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
+        <v>460.8</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -2766,41 +3453,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="D37" s="10" t="n">
+        <v>1120.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>21816.4</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>219.8</v>
+      </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>118.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>1082.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>4920.8</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>1102.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>101.9</v>
+      </c>
       <c r="T37" s="3" t="n">
-        <v>26.4</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="X37" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y37" s="3" t="inlineStr"/>
-      <c r="Z37" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>231.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2815,59 +3536,73 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="9" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="8" t="n">
-        <v>48.6</v>
+      <c r="D38" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>41.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>15.4</v>
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>95.09999999999999</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>866.1</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>92420.8</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
       <c r="P38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="8" t="n">
-        <v>148.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="n">
-        <v>3931.2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2881,55 +3616,75 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>42.1</v>
+        <v>46.8</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="M39" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>898.6</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
+        <v>40.8</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>92.8</v>
+      </c>
       <c r="T39" s="3" t="n">
-        <v>57.7</v>
+        <v>86.8</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
+        <v>18.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>29.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>69.8</v>
+      </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -2944,44 +3699,74 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="8" t="n">
-        <v>19.8</v>
+      <c r="P40" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>26</v>
+        <v>91.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>18.6</v>
+      <c r="X40" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>69.2</v>
+        <v>81.5</v>
       </c>
       <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -2997,42 +3782,74 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>840.1</v>
+        <v>81</v>
       </c>
       <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="W41" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>14.5</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>242.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>76.5</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3046,36 +3863,74 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="J42" s="8" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>8540.1</v>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
-      <c r="X42" s="3" t="inlineStr"/>
-      <c r="Y42" s="3" t="inlineStr"/>
-      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3090,39 +3945,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="D43" s="12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>18.5</v>
+      </c>
       <c r="H43" s="8" t="n">
-        <v>172.2</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O43" s="3" t="inlineStr"/>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>9.4</v>
+      </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+        <v>29.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y43" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z43" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3138,35 +4029,41 @@
       </c>
       <c r="C44" s="3" t="inlineStr"/>
       <c r="D44" s="9" t="n">
-        <v>90</v>
+        <v>18.1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>112</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I44" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N44" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="O44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="n">
+        <v>80.8</v>
+      </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -3174,14 +4071,24 @@
       <c r="R44" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
+      <c r="U44" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -3199,52 +4106,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="12" t="inlineStr"/>
-      <c r="F45" s="12" t="inlineStr"/>
-      <c r="G45" s="9" t="n">
-        <v>16.2</v>
+      <c r="C45" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>60</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.8</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>109.6</v>
+        <v>1189.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>1102.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>17992.6</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1656</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1662</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>217.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>322.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>169.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3261,21 +4190,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="E46" s="10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -3284,32 +4215,44 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="8" t="n">
+      <c r="S46" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="n">
+        <v>23.8</v>
+      </c>
       <c r="W46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>69.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>10.7</v>
+        <v>119.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,10 +161,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -771,9 +783,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="12" t="n">
         <v>27.8</v>
       </c>
@@ -787,7 +797,7 @@
         <v>9.6</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -798,9 +808,11 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="8" t="n">
-        <v>16.8</v>
+      <c r="L4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18.1</v>
@@ -809,16 +821,16 @@
         <v>84</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>513.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>28.5</v>
+        <v>20.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
@@ -869,11 +881,11 @@
       <c r="K5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>128.9</v>
+      <c r="L5" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
@@ -881,9 +893,7 @@
       <c r="O5" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
@@ -894,7 +904,7 @@
         <v>21.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -902,14 +912,14 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>56.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>13.6</v>
@@ -929,9 +939,9 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E6" s="9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="F6" s="9" t="n">
@@ -953,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10.4</v>
+        <v>18.4</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>16.8</v>
@@ -965,7 +975,7 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>28.6</v>
@@ -977,7 +987,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>656.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1030,16 +1040,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>484.1</v>
+        <v>7.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
@@ -1047,7 +1057,9 @@
       <c r="O7" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -1058,25 +1070,25 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81.8</v>
+        <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1093,26 +1105,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E8" s="11" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19.4</v>
+      <c r="H8" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="n">
@@ -1135,12 +1147,12 @@
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1173,20 +1185,18 @@
       <c r="E9" s="10" t="n">
         <v>88.7</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>115.2</v>
-      </c>
+      <c r="F9" s="13" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>57.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>26.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1195,46 +1205,46 @@
         <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>42.3</v>
+        <v>423.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>142.8</v>
+        <v>192.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>100.8</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2099.1</v>
+        <v>263.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>992.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.7</v>
+        <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>11.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>19.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>615</v>
+        <v>68</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1250,20 +1260,20 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="10" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>13.4</v>
+      <c r="D10" s="12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>11.3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
@@ -1272,10 +1282,10 @@
         <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1287,7 +1297,7 @@
         <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1299,7 +1309,7 @@
         <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1314,7 +1324,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.9</v>
@@ -1333,23 +1343,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="12" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F11" s="12" t="n">
+      <c r="D11" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>11.6</v>
+      <c r="G11" s="3" t="n">
+        <v>41.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5.4</v>
+        <v>54.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1360,20 +1370,20 @@
       <c r="L11" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>1.8</v>
+      <c r="M11" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.9</v>
+        <v>82</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q11" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>20</v>
@@ -1382,7 +1392,7 @@
         <v>18.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.8</v>
+        <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1403,9 +1413,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>51.3</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="12" t="n">
         <v>28.2</v>
       </c>
@@ -1437,7 +1445,7 @@
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
@@ -1446,16 +1454,16 @@
         <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
@@ -1464,14 +1472,14 @@
       <c r="W12" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="X12" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1486,9 +1494,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="12" t="n">
         <v>26</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>41.2</v>
+        <v>17.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1511,22 +1517,22 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>283.5</v>
+        <v>23.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>41.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1535,15 +1541,15 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>51.1</v>
+        <v>57.1</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V13" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1553,11 +1559,9 @@
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1581,16 +1585,14 @@
       <c r="F14" s="12" t="n">
         <v>23.3</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>8.199999999999999</v>
-      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="n">
-        <v>27.8</v>
+        <v>47.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1602,8 +1604,8 @@
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>87.8</v>
+      <c r="N14" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>74.5</v>
@@ -1611,32 +1613,32 @@
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>86.8</v>
+      <c r="Q14" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>3.4</v>
+        <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1656,10 +1658,10 @@
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="12" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>23.3</v>
@@ -1677,8 +1679,8 @@
         <v>10.2</v>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+      <c r="L15" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1687,10 +1689,10 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1736,53 +1738,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
-        <v>138.2</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>113.9</v>
+      <c r="D16" s="10" t="n">
+        <v>1038.8</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
+        <v>1113.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>22</v>
+        <v>3019.1</v>
       </c>
       <c r="I16" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>900.6</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>980.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>920</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>2281.2</v>
+        <v>838.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>104.1</v>
+        <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>266.2</v>
@@ -1791,19 +1789,19 @@
         <v>86.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>152.8</v>
+        <v>122.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>94.5</v>
+        <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>92.3</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>304.8</v>
+        <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.1</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1818,23 +1816,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="10" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1846,23 +1842,23 @@
       <c r="L17" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>13.8</v>
@@ -1871,19 +1867,19 @@
         <v>52.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.8</v>
+        <v>1.7</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>18.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>12.2</v>
@@ -1901,56 +1897,52 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H18" s="8" t="n">
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>12.6</v>
+      <c r="J18" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>62.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>14.6</v>
+        <v>78.8</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>21.8</v>
+        <v>30.4</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>48.8</v>
@@ -1959,7 +1951,7 @@
         <v>22.2</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>26.4</v>
+        <v>46.4</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.2</v>
@@ -1982,7 +1974,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D19" s="12" t="n">
         <v>29.8</v>
       </c>
@@ -1996,7 +1990,7 @@
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -2005,23 +1999,23 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2030,13 +2024,13 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>96.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.1</v>
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2045,10 +2039,10 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>19.9</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2065,32 +2059,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="12" t="n">
-        <v>33.3</v>
+        <v>30.6</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>117.4</v>
+      <c r="M20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>19</v>
@@ -2114,7 +2108,7 @@
         <v>48.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
@@ -2126,7 +2120,7 @@
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>14.4</v>
@@ -2145,16 +2139,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E21" s="12" t="n">
+      <c r="D21" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G21" s="12" t="n">
+      <c r="F21" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2164,19 +2158,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2192,10 +2186,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2203,11 +2197,11 @@
       <c r="W21" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="X21" s="8" t="n">
-        <v>18.8</v>
+      <c r="X21" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2226,14 +2220,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="12" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>23.5</v>
+      <c r="D22" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.8</v>
@@ -2272,7 +2266,7 @@
         <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2280,15 +2274,17 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="n">
+        <v>155.1</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>5.7</v>
@@ -2306,77 +2302,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>117.5</v>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>117.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>529.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>22.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>926.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>140.4</v>
+        <v>44</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.4</v>
+        <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1180.4</v>
+        <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>267.9</v>
+        <v>8267.799999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.6</v>
+        <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>41.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2216.1</v>
+        <v>205.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>24.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2391,23 +2385,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="12" t="n">
-        <v>29.9</v>
+        <v>29.1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>12.1</v>
+      <c r="G24" s="12" t="n">
+        <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2415,7 +2407,9 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.7</v>
@@ -2453,7 +2447,7 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>12.9</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>61</v>
@@ -2474,66 +2468,62 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>23</v>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>2.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>56.9</v>
+        <v>10.8</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>221.8</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.9</v>
+        <v>662.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>19.8</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
@@ -2552,28 +2542,28 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>10.2</v>
+      <c r="E26" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2584,11 +2574,9 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>48.4</v>
-      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>69.8</v>
+        <v>6</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>3</v>
@@ -2606,10 +2594,10 @@
         <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>29.4</v>
+        <v>43.8</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>18.6</v>
@@ -2618,10 +2606,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>38.5</v>
+        <v>18.6</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2637,31 +2625,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G27" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.9</v>
+        <v>68.7</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
@@ -2669,16 +2657,18 @@
       <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <v>21.8</v>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>188.9</v>
+        <v>22.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
       </c>
@@ -2686,7 +2676,7 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>12.8</v>
@@ -2716,14 +2706,14 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>19.8</v>
+      <c r="D28" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
@@ -2743,25 +2733,25 @@
       <c r="L28" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>17.8</v>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>5294</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
@@ -2841,13 +2831,13 @@
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>659.5</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.2</v>
+        <v>152.5</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
@@ -2855,8 +2845,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>12.8</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2877,27 +2867,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>109.5</v>
+      <c r="C30" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>1334.8</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>109.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2016.1</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2681.4</v>
+        <v>32.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>90.40000000000001</v>
@@ -2906,22 +2898,22 @@
         <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>836.5</v>
+        <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19</v>
+        <v>904.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>420</v>
+        <v>43464.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1082</v>
+        <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>102.2</v>
@@ -2930,22 +2922,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1818.2</v>
+        <v>118.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>985.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>418.1</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>316.2</v>
+        <v>3136.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>49.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2961,7 +2953,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>26.6</v>
@@ -2979,14 +2971,16 @@
         <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>85.2</v>
+      </c>
       <c r="L31" s="8" t="n">
-        <v>318.3</v>
+        <v>18.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
@@ -3025,7 +3019,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>69.2</v>
+        <v>475.1</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>10</v>
@@ -3043,20 +3037,16 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="9" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>18.9</v>
+        <v>0.9</v>
+      </c>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>15.2</v>
@@ -3080,37 +3070,37 @@
         <v>18.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3126,16 +3116,14 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F33" s="9" t="n">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3145,10 +3133,10 @@
         <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3157,21 +3145,21 @@
         <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3186,7 +3174,7 @@
       <c r="V33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3210,16 +3198,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="9" t="n">
-        <v>24.2</v>
+      <c r="D34" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G34" s="8" t="n">
+      <c r="F34" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3244,15 +3232,15 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3264,14 +3252,14 @@
       <c r="U34" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>284.6</v>
+      <c r="V34" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
@@ -3289,7 +3277,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>28.6</v>
@@ -3306,8 +3294,8 @@
       <c r="H35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <v>11</v>
+      <c r="I35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3325,16 +3313,16 @@
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>190.8</v>
+        <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
@@ -3348,7 +3336,7 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3369,26 +3357,24 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>8</v>
@@ -3400,7 +3386,7 @@
         <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3424,7 +3410,7 @@
         <v>26.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>460.8</v>
+        <v>17</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3454,73 +3440,73 @@
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="10" t="n">
-        <v>1120.8</v>
+        <v>1138.8</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>80.2</v>
+        <v>88.2</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>99.59999999999999</v>
+      <c r="G37" s="9" t="n">
+        <v>49.9</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>808</v>
+        <v>898</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21816.4</v>
+        <v>210.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>219.8</v>
+        <v>31.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>118.2</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>11.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1082.2</v>
+        <v>82.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>4920.8</v>
+        <v>12.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>14.9</v>
+        <v>44.5</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1102.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.9</v>
+        <v>10.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>288.6</v>
+        <v>208.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>14.1</v>
+        <v>44.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>106.8</v>
+        <v>156</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>231.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3536,13 +3522,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="12" t="n">
         <v>26.8</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="12" t="n">
         <v>22.2</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3555,15 +3541,15 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3582,16 +3568,16 @@
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>88.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>38.7</v>
+        <v>57.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
+        <v>240.1</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>19</v>
@@ -3616,74 +3602,70 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46.8</v>
+        <v>4.8</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>36.1</v>
+        <v>3.8</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19</v>
+      <c r="M39" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>898.6</v>
+        <v>8.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>40.8</v>
-      </c>
+      <c r="R39" s="3" t="inlineStr"/>
       <c r="S39" s="8" t="n">
-        <v>92.8</v>
+        <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86.8</v>
+        <v>26</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>10.6</v>
+        <v>18.6</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>69.8</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3700,31 +3682,29 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E40" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>16.4</v>
+      <c r="F40" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3739,19 +3719,19 @@
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
+        <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>91.8</v>
+        <v>51.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>14.4</v>
@@ -3783,40 +3763,40 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>25.4</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>43.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
@@ -3828,12 +3808,14 @@
       <c r="R41" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="T41" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>108.4</v>
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19.6</v>
@@ -3842,7 +3824,7 @@
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>76.5</v>
@@ -3863,28 +3845,26 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="I42" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
@@ -3895,7 +3875,7 @@
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3907,7 +3887,7 @@
         <v>28.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
@@ -3919,17 +3899,17 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X42" s="8" t="n">
+      <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>57</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3945,23 +3925,21 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="12" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E43" s="12" t="n">
+      <c r="D43" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="F43" s="14" t="inlineStr"/>
       <c r="G43" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
@@ -3984,25 +3962,25 @@
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="8" t="n">
-        <v>9.4</v>
+      <c r="Q43" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="S43" s="8" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>29.9</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="8" t="n">
+      <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4027,15 +4005,17 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="D44" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E44" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>30</v>
+        <v>21.7</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
@@ -4044,17 +4024,19 @@
         <v>15.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K44" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>26.5</v>
+      <c r="M44" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N44" s="8" t="n">
         <v>16.4</v>
@@ -4063,7 +4045,7 @@
         <v>80.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -4077,14 +4059,12 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="8" t="n">
-        <v>20.8</v>
+      <c r="W44" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4106,56 +4086,52 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>288.4</v>
+        <v>830.6</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1189.6</v>
+        <v>1089.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1102.7</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>17992.6</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1662</v>
+        <v>650.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>121</v>
+        <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>11.6</v>
+        <v>746.4</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>217.9</v>
@@ -4164,13 +4140,13 @@
         <v>107.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>192.8</v>
+        <v>12.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>112</v>
+        <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>322.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4190,23 +4166,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
-        <v>27.9</v>
+      <c r="D46" s="9" t="n">
+        <v>61.9</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G46" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -4215,11 +4191,11 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="M46" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
@@ -4228,19 +4204,19 @@
         <v>3.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>23</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>23.8</v>
@@ -4252,7 +4228,7 @@
         <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>119.4</v>
+        <v>165.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -808,7 +808,7 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>1.8</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -823,23 +823,23 @@
       <c r="P4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="12" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S4" s="3" t="n">
+      <c r="R4" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S4" s="12" t="n">
         <v>20.5</v>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="12" t="n">
         <v>54.8</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="14" t="inlineStr"/>
+      <c r="W4" s="12" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -894,25 +894,25 @@
         <v>83</v>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>16.8</v>
+      <c r="S5" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T5" s="12" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="U5" s="12" t="n">
+        <v>12.9</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -962,49 +962,49 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X6" s="3" t="n">
+      <c r="S6" s="12" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T6" s="12" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="U6" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W6" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X6" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="Z6" s="12" t="n">
         <v>10.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1060,25 +1060,25 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="S7" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="T7" s="12" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="U7" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V7" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1126,7 +1126,7 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
@@ -1137,25 +1137,25 @@
         <v>81</v>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="12" t="n">
         <v>21.2</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>24.2</v>
+      <c r="S8" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="T8" s="12" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="U8" s="12" t="n">
+        <v>18.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1198,13 +1198,13 @@
       <c r="J9" s="3" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1216,10 +1216,10 @@
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>192.8</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="10" t="n">
         <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1231,10 +1231,10 @@
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>127.2</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1284,10 +1284,10 @@
       <c r="K10" s="3" t="n">
         <v>51.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1299,25 +1299,25 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="12" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="12" t="n">
         <v>21.2</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V10" s="3" t="n">
+      <c r="S10" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="T10" s="12" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="U10" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="V10" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="12" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1385,7 +1385,7 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1395,8 +1395,8 @@
         <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="12" t="inlineStr"/>
+      <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
       <c r="P12" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1466,20 +1466,20 @@
         <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="X12" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>13.8</v>
+      <c r="X12" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Y12" s="12" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="Z12" s="12" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
       <c r="Q13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1549,19 +1549,21 @@
       <c r="U13" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="X13" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v>764</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="X13" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="Z13" s="12" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1616,7 +1618,7 @@
       <c r="Q14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1628,20 +1630,20 @@
       <c r="U14" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>10.6</v>
+      <c r="X14" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Z14" s="12" t="n">
+        <v>7.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1678,7 +1680,7 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
       <c r="L15" s="3" t="n">
         <v>11.8</v>
       </c>
@@ -1697,7 +1699,7 @@
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1709,20 +1711,20 @@
       <c r="U15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="12" t="n">
         <v>25.4</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="X15" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+      <c r="X15" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="Z15" s="12" t="n">
+        <v>10.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1757,13 +1759,13 @@
       <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1773,10 +1775,10 @@
         <v>5.7</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="10" t="n">
         <v>838.2</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="10" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1788,10 +1790,10 @@
       <c r="U16" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="10" t="n">
         <v>122.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="10" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1839,10 +1841,10 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1854,10 +1856,10 @@
       <c r="P17" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1869,20 +1871,20 @@
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>12.2</v>
+      <c r="X17" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z17" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1923,7 +1925,7 @@
       <c r="L18" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1935,25 +1937,25 @@
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="S18" s="3" t="n">
+      <c r="R18" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="S18" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="T18" s="3" t="n">
+      <c r="T18" s="12" t="n">
         <v>48.8</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>46.4</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>20.2</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2004,7 +2006,7 @@
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2032,7 +2034,7 @@
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2083,7 +2085,7 @@
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2113,7 +2115,7 @@
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2163,10 +2165,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2178,7 +2180,7 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="Q21" s="14" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2194,7 +2196,7 @@
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2247,7 +2249,7 @@
       <c r="L22" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2277,7 +2279,7 @@
       <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2324,13 +2326,13 @@
       <c r="J23" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="10" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2342,10 +2344,10 @@
       <c r="P23" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="10" t="n">
         <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2357,10 +2359,10 @@
       <c r="U23" s="3" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>123.5</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="10" t="n">
         <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2410,25 +2412,25 @@
       <c r="K24" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N24" s="3" t="n">
+      <c r="M24" s="12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N24" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" s="12" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="P24" s="12" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2440,10 +2442,10 @@
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2508,8 +2510,8 @@
       <c r="P25" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="n">
+      <c r="Q25" s="14" t="inlineStr"/>
+      <c r="R25" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2522,7 +2524,7 @@
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
@@ -2584,7 +2586,7 @@
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2596,10 +2598,10 @@
       <c r="U26" s="3" t="n">
         <v>43.8</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="9" t="n">
         <v>49.4</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2666,10 +2668,10 @@
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2684,7 +2686,7 @@
       <c r="V27" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2745,25 +2747,25 @@
       <c r="P28" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="12" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S28" s="3" t="n">
+      <c r="R28" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S28" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="T28" s="3" t="n">
+      <c r="T28" s="12" t="n">
         <v>56.7</v>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="U28" s="12" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2809,25 +2811,25 @@
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="M29" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N29" s="3" t="n">
+      <c r="M29" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N29" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="P29" s="12" t="n">
         <v>2.4</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2842,7 +2844,7 @@
       <c r="V29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2891,13 +2893,13 @@
       <c r="J30" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="10" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2909,10 +2911,10 @@
       <c r="P30" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="12" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2924,10 +2926,10 @@
       <c r="U30" s="3" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="10" t="n">
         <v>118.2</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -2979,25 +2981,25 @@
       <c r="K31" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="M31" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" s="12" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3009,10 +3011,10 @@
       <c r="U31" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3060,7 +3062,7 @@
       <c r="K32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3078,7 +3080,7 @@
       <c r="Q32" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3090,19 +3092,21 @@
       <c r="U32" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="X32" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+      <c r="X32" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y32" s="12" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Z32" s="12" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3141,10 +3145,10 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3156,34 +3160,36 @@
       <c r="P33" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S33" s="3" t="n">
+      <c r="Q33" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R33" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S33" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="12" t="n">
         <v>15.3</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="X33" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Y33" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3222,7 +3228,7 @@
       <c r="K34" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3237,32 +3243,36 @@
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="12" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S34" s="3" t="n">
+      <c r="R34" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="S34" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="12" t="n">
         <v>57.2</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="12" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Y34" s="3" t="inlineStr"/>
-      <c r="Z34" s="3" t="inlineStr"/>
+      <c r="X34" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Y34" s="12" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Z34" s="12" t="n">
+        <v>7.6</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3303,7 +3313,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3318,32 +3328,36 @@
       <c r="P35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="S35" s="3" t="n">
+      <c r="Q35" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S35" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="T35" s="3" t="n">
+      <c r="T35" s="12" t="n">
         <v>62.2</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U35" s="12" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y35" s="3" t="inlineStr"/>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="X35" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y35" s="12" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Z35" s="12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3382,25 +3396,25 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N36" s="3" t="n">
+      <c r="M36" s="12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N36" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="O36" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="P36" s="12" t="n">
         <v>2.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3412,19 +3426,21 @@
       <c r="U36" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="X36" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y36" s="12" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Z36" s="12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3460,13 +3476,13 @@
       <c r="J37" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="12" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="10" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3478,10 +3494,10 @@
       <c r="P37" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="12" t="n">
         <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3493,10 +3509,10 @@
       <c r="U37" s="3" t="n">
         <v>44.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="12" t="n">
         <v>109.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3546,25 +3562,25 @@
       <c r="K38" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N38" s="3" t="n">
+      <c r="M38" s="12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O38" s="12" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="P38" s="12" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3576,10 +3592,10 @@
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="10" t="n">
         <v>240.1</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3627,7 +3643,7 @@
       <c r="K39" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3645,7 +3661,7 @@
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="inlineStr"/>
+      <c r="R39" s="14" t="inlineStr"/>
       <c r="S39" s="8" t="n">
         <v>19.8</v>
       </c>
@@ -3655,7 +3671,7 @@
       <c r="U39" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3706,19 +3722,19 @@
       <c r="K40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="12" t="n">
         <v>19.2</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P40" s="3" t="n">
+      <c r="N40" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O40" s="12" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="P40" s="12" t="n">
         <v>2.6</v>
       </c>
       <c r="Q40" s="3" t="n">
@@ -3736,7 +3752,7 @@
       <c r="U40" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3789,10 +3805,10 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>1.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3817,7 +3833,7 @@
       <c r="U41" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3868,7 +3884,7 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3886,7 +3902,7 @@
       <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -3896,7 +3912,7 @@
       <c r="U42" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W42" s="3" t="n">
@@ -3947,7 +3963,7 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="12" t="n">
         <v>16.4</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -3977,19 +3993,19 @@
       <c r="U43" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="12" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X43" s="3" t="n">
+      <c r="W43" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X43" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y43" s="3" t="n">
+      <c r="Y43" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="Z43" s="3" t="n">
+      <c r="Z43" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4032,7 +4048,7 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
@@ -4060,7 +4076,7 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4108,13 +4124,13 @@
       <c r="J45" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="10" t="n">
         <v>1089.6</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4124,10 +4140,10 @@
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="10" t="n">
         <v>650.2</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4139,10 +4155,10 @@
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="10" t="n">
         <v>12.8</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="10" t="n">
         <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4188,10 +4204,10 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4203,10 +4219,10 @@
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4218,10 +4234,10 @@
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,25 +146,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,20 +796,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E4" s="12" t="n">
+      <c r="D4" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -805,41 +817,39 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>6.8</v>
+      <c r="L4" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>86.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q4" s="13" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q4" s="12" t="n">
+      <c r="R4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S4" s="12" t="n">
+      <c r="S4" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="T4" s="12" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U4" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="14" t="inlineStr"/>
-      <c r="W4" s="12" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="11" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -856,17 +866,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -878,50 +890,52 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.4</v>
+      <c r="K5" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="12" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="12" t="n">
+      <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="12" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="U5" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="S5" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="V5" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="12" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="11" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X5" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y5" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Y5" s="11" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Z5" s="11" t="n">
         <v>13.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -937,17 +951,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="C6" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="F6" s="11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -959,52 +975,52 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M6" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="12" t="n">
+      <c r="M6" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="O6" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="P6" s="12" t="n">
+      <c r="O6" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S6" s="12" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T6" s="12" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="U6" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="V6" s="12" t="n">
+      <c r="S6" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="V6" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="X6" s="12" t="n">
+      <c r="X6" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" s="11" t="n">
         <v>10.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1020,17 +1036,19 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="12" t="n">
+      <c r="C7" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1040,55 +1058,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>7.4</v>
+      <c r="L7" s="13" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R7" s="12" t="n">
+      <c r="Q7" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="S7" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="T7" s="12" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="U7" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W7" s="12" t="n">
+      <c r="S7" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>14.9</v>
+      <c r="X7" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Y7" s="11" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Z7" s="11" t="n">
+        <v>10.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1104,31 +1122,35 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
-        <v>22.9</v>
+      <c r="D8" s="11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>23.59</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="14" t="inlineStr"/>
+      <c r="L8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="M8" s="3" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1136,34 +1158,38 @@
       <c r="O8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="12" t="n">
+      <c r="P8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S8" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="T8" s="12" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="U8" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="W8" s="12" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="n">
-        <v>14.8</v>
+      <c r="S8" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V8" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X8" s="11" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Y8" s="11" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="Z8" s="11" t="n">
+        <v>10.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1179,36 +1205,38 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="10" t="n">
-        <v>142.8</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
+      <c r="D9" s="11" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>116.9</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K9" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="20" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="20" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>423.5</v>
@@ -1216,35 +1244,35 @@
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" s="10" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="R9" s="10" t="n">
-        <v>186</v>
+      <c r="Q9" s="20" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="R9" s="20" t="n">
+        <v>1196</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>102.6</v>
+        <v>182.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>263.1</v>
+        <v>9255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="V9" s="10" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="W9" s="10" t="n">
-        <v>97.40000000000001</v>
+      <c r="V9" s="11" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="W9" s="11" t="n">
+        <v>73.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>229.9</v>
+        <v>26.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1260,17 +1288,17 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>23.4</v>
       </c>
-      <c r="G10" s="12" t="n">
-        <v>11.3</v>
+      <c r="G10" s="11" t="n">
+        <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>16.5</v>
@@ -1279,15 +1307,15 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="20" t="n">
         <v>18.8</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="20" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1299,35 +1327,35 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="20" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="20" t="n">
         <v>21.2</v>
       </c>
-      <c r="S10" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="T10" s="12" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="U10" s="12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="V10" s="10" t="n">
+      <c r="S10" s="3" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V10" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>13.9</v>
+      <c r="X10" s="11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Y10" s="11" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Z10" s="11" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1343,23 +1371,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="D11" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.2</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.6</v>
+        <v>15.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1367,38 +1395,48 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R11" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="R11" s="11" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="12" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
+        <v>425.4</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="W11" s="13" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>48.9</v>
+      </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1413,17 +1451,19 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="12" t="n">
+      <c r="C12" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1438,10 +1478,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1451,35 +1491,37 @@
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q12" s="13" t="n">
         <v>2.8</v>
       </c>
-      <c r="R12" s="12" t="n">
+      <c r="R12" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="12" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W12" s="12" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z12" s="3" t="n">
         <v>19.8</v>
-      </c>
-      <c r="X12" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y12" s="12" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="Z12" s="12" t="n">
-        <v>9.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1495,20 +1537,20 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1517,52 +1559,52 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>23.5</v>
+        <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V13" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X13" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y13" s="12" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="Z13" s="12" t="n">
-        <v>9.699999999999999</v>
+      <c r="W13" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1578,39 +1620,41 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="11" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>47.8</v>
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="14" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>714.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1618,32 +1662,32 @@
       <c r="Q14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>19.6</v>
+      <c r="R14" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="S14" s="14" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>51.5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V14" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W14" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="X14" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y14" s="12" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="Z14" s="12" t="n">
-        <v>7.6</v>
+      <c r="X14" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1659,16 +1703,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="11" t="n">
         <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1680,26 +1724,28 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N15" s="3" t="n">
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N15" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="O15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>13.4</v>
+      <c r="O15" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>3.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="12" t="n">
+      <c r="R15" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1709,22 +1755,22 @@
         <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="W15" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X15" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="Z15" s="12" t="n">
-        <v>10.8</v>
+      <c r="W15" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1739,71 +1785,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
-        <v>1038.8</v>
-      </c>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
-        <v>1113.9</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="C16" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3019.1</v>
+        <v>288.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="K16" s="10" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="K16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>84</v>
+      <c r="L16" s="11" t="n">
+        <v>93</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>84.09999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>909.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="10" t="n">
-        <v>838.2</v>
-      </c>
-      <c r="R16" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="Q16" s="20" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="R16" s="11" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>266.2</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="20" t="n">
         <v>122.8</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="20" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1819,20 +1871,20 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="10" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E17" s="3" t="n">
+      <c r="D17" s="11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>0.1</v>
+      <c r="G17" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1841,50 +1893,50 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>18.1</v>
+      <c r="N17" s="14" t="n">
+        <v>19.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q17" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q17" s="20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R17" s="11" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="20" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y17" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z17" s="12" t="n">
-        <v>9</v>
+      <c r="W17" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>1068.5</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>810.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1899,70 +1951,78 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="3" t="n">
-        <v>8.4</v>
+      <c r="C18" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>24.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.1</v>
+        <v>13.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>13.6</v>
+        <v>456.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>13.6</v>
+        <v>126.1</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>17.8</v>
+        <v>4.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>78.8</v>
+        <v>138.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R18" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="Q18" s="13" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="T18" s="12" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="U18" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="W18" s="12" t="n">
-        <v>20.2</v>
+      <c r="T18" s="3" t="n">
+        <v>457.1</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>38</v>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1976,23 +2036,21 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E19" s="12" t="n">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -2001,50 +2059,52 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>18.7</v>
+      <c r="N19" s="14" t="n">
+        <v>18.1</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="S19" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="T19" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
+      <c r="T19" s="11" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U19" s="11" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="12" t="n">
+      <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>24</v>
+        <v>294</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2059,22 +2119,26 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="12" t="n">
+      <c r="C20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="8" t="n">
-        <v>17.4</v>
+      <c r="G20" s="11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
@@ -2085,7 +2149,7 @@
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2097,35 +2161,35 @@
       <c r="P20" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S20" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>76</v>
+      <c r="T20" s="11" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="U20" s="11" t="n">
+        <v>23</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2141,16 +2205,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="11" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="F21" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G21" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2160,19 +2224,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M21" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M21" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>19</v>
+      <c r="N21" s="11" t="n">
+        <v>19.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2180,7 +2244,9 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="14" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2188,22 +2254,22 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>256</v>
+        <v>56.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="12" t="n">
+      <c r="W21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2221,17 +2287,19 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="n">
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="11" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2247,13 +2315,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M22" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="M22" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2261,35 +2329,35 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T22" s="3" t="n">
+      <c r="R22" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T22" s="11" t="n">
         <v>68.3</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="12" t="n">
+      <c r="W22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>155.1</v>
+        <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.7</v>
+        <v>254.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2304,75 +2372,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>117.8</v>
+      <c r="C23" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>117.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.2</v>
+        <v>36.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>529.5</v>
+        <v>311.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="K23" s="20" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>88</v>
+      <c r="L23" s="20" t="n">
+        <v>92</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q23" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="R23" s="10" t="n">
-        <v>103.9</v>
+        <v>15.6</v>
+      </c>
+      <c r="Q23" s="20" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="R23" s="20" t="n">
+        <v>103.4</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8267.799999999999</v>
+        <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="V23" s="10" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W23" s="10" t="n">
-        <v>25.6</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="V23" s="20" t="n">
+        <v>1123.5</v>
+      </c>
+      <c r="W23" s="20" t="n">
+        <v>935.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94.8</v>
+        <v>26</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>205.4</v>
+        <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.8</v>
+        <v>652.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2388,20 +2458,20 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2409,53 +2479,51 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L24" s="12" t="n">
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="20" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="O24" s="12" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P24" s="12" t="n">
+      <c r="M24" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="R24" s="10" t="n">
+      <c r="Q24" s="20" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="R24" s="20" t="n">
         <v>20.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="V24" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W24" s="12" t="n">
-        <v>19.1</v>
+        <v>1.8</v>
+      </c>
+      <c r="V24" s="20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W24" s="20" t="n">
+        <v>10.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>12.9</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>118.9</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2470,21 +2538,23 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.6</v>
+      <c r="C25" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2496,40 +2566,48 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="14" t="inlineStr"/>
-      <c r="R25" s="12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q25" s="13" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="R25" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>662.3</v>
+        <v>405.5</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>12.8</v>
+        <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2543,29 +2621,27 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>16</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="11" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>16.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2576,42 +2652,44 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="12" t="n">
+      <c r="R26" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>12.2</v>
+        <v>52.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="W26" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>18.6</v>
+        <v>28.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>19.8</v>
+        <v>112.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2626,74 +2704,76 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>12.8</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>68.7</v>
+        <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R27" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S27" s="3" t="n">
+      <c r="Q27" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S27" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W27" s="12" t="n">
+      <c r="T27" s="11" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U27" s="11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="V27" s="13" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2707,72 +2787,78 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="C28" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G28" s="11" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="14" t="n">
+        <v>66</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3" t="n">
+      <c r="M28" s="11" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N28" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="P28" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q28" s="12" t="n">
+      <c r="Q28" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="12" t="n">
+      <c r="R28" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="S28" s="12" t="n">
+      <c r="S28" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="T28" s="12" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="U28" s="12" t="n">
+      <c r="T28" s="11" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="U28" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>19.8</v>
+        <v>29.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2786,69 +2872,71 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="12" t="n">
+      <c r="C29" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G29" s="12" t="n">
+      <c r="E29" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="14" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L29" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M29" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="N29" s="12" t="n">
+      <c r="N29" s="11" t="n">
         <v>19.1</v>
       </c>
-      <c r="O29" s="12" t="n">
+      <c r="O29" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="P29" s="12" t="n">
+      <c r="P29" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>152.5</v>
+      <c r="R29" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S29" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="U29" s="11" t="n">
+        <v>13.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="W29" s="12" t="n">
+      <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>19.8</v>
+      <c r="X29" s="14" t="n">
+        <v>19</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2869,52 +2957,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1334.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="11" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="E30" s="20" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>48.4</v>
+      <c r="F30" s="11" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>185.4</v>
+        <v>39.8</v>
+      </c>
+      <c r="K30" s="20" t="n">
+        <v>308.4</v>
+      </c>
+      <c r="L30" s="20" t="n">
+        <v>9434.799999999999</v>
+      </c>
+      <c r="M30" s="20" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>904.6</v>
+        <v>90.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43464.4</v>
+        <v>681.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="20" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="12" t="n">
+      <c r="R30" s="20" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2924,22 +3010,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="V30" s="10" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="W30" s="10" t="n">
-        <v>99.59999999999999</v>
+        <v>10.8</v>
+      </c>
+      <c r="V30" s="20" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="W30" s="20" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>418.1</v>
+        <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>3136.2</v>
+        <v>916.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.6</v>
+        <v>47.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2955,22 +3041,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>9.9</v>
+      <c r="G31" s="11" t="n">
+        <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26.1</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -2978,29 +3064,27 @@
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="P31" s="12" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="20" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M31" s="20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="20" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>20.4</v>
+      <c r="R31" s="20" t="n">
+        <v>18.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3009,22 +3093,22 @@
         <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V31" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" s="20" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="12" t="n">
+      <c r="W31" s="20" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>475.1</v>
+        <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3040,72 +3124,68 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E32" s="14" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
+      <c r="D32" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>19.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>15.2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R32" s="12" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X32" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y32" s="12" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="Z32" s="12" t="n">
-        <v>5.7</v>
+        <v>96.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="V32" s="11" t="inlineStr"/>
+      <c r="W32" s="13" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>4412.8</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3121,16 +3201,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="D33" s="11" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G33" s="11" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3140,55 +3220,55 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O33" s="3" t="n">
+      <c r="M33" s="11" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O33" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="P33" s="11" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q33" s="12" t="n">
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R33" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S33" s="12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T33" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="U33" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V33" s="12" t="n">
+      <c r="R33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V33" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="12" t="n">
+      <c r="W33" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X33" s="12" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="Y33" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z33" s="12" t="n">
-        <v>4.7</v>
+      <c r="X33" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3204,17 +3284,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>1.7</v>
+      <c r="D34" s="13" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>1.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>16.6</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17</v>
@@ -3226,9 +3306,9 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L34" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3238,40 +3318,40 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="12" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="S34" s="12" t="n">
+      <c r="R34" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S34" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="T34" s="12" t="n">
+      <c r="T34" s="3" t="n">
         <v>57.2</v>
       </c>
-      <c r="U34" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V34" s="12" t="n">
+      <c r="U34" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="V34" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="12" t="n">
+      <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X34" s="12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Y34" s="12" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="Z34" s="12" t="n">
-        <v>7.6</v>
+      <c r="X34" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3286,20 +3366,18 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>10.8</v>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
@@ -3313,50 +3391,50 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>17.6</v>
+      <c r="L35" s="11" t="n">
+        <v>17.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q35" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R35" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S35" s="12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="T35" s="12" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U35" s="12" t="n">
+      <c r="T35" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="12" t="n">
+      <c r="V35" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="12" t="n">
+      <c r="W35" s="14" t="n">
         <v>18.8</v>
       </c>
-      <c r="X35" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y35" s="12" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z35" s="12" t="n">
-        <v>2.3</v>
+      <c r="X35" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3372,16 +3450,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="12" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G36" s="12" t="n">
+      <c r="D36" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G36" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3396,51 +3474,49 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M36" s="12" t="n">
+      <c r="L36" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M36" s="11" t="n">
         <v>16.5</v>
       </c>
-      <c r="N36" s="12" t="n">
+      <c r="N36" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="O36" s="12" t="n">
+      <c r="O36" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="P36" s="12" t="n">
+      <c r="P36" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="12" t="n">
+      <c r="R36" s="14" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>26.4</v>
+        <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V36" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="12" t="n">
+      <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y36" s="12" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z36" s="12" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="X36" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3455,71 +3531,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="10" t="n">
-        <v>1138.8</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>111</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>49.9</v>
+      <c r="D37" s="20" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>8821.799999999999</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>898</v>
+        <v>87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>210.9</v>
+        <v>40.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K37" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>82.59999999999999</v>
+        <v>31.5</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="M37" s="20" t="n">
+        <v>4.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>12.6</v>
+        <v>20.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>132.8</v>
-      </c>
-      <c r="R37" s="12" t="n">
-        <v>102.2</v>
+        <v>149.4</v>
+      </c>
+      <c r="Q37" s="20" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="R37" s="20" t="n">
+        <v>1082.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>10.1</v>
+        <v>1181.5</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>208.6</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="V37" s="12" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="W37" s="10" t="n">
-        <v>18.4</v>
+        <v>79.8</v>
+      </c>
+      <c r="V37" s="11" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="W37" s="20" t="n">
+        <v>998.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3538,17 +3614,17 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="20" t="n">
         <v>26.8</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="20" t="n">
         <v>17.6</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="20" t="n">
         <v>22.2</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>92.09999999999999</v>
+      <c r="G38" s="11" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>17</v>
@@ -3557,54 +3633,54 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="O38" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M38" s="20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="P38" s="12" t="n">
+      <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="20" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="12" t="n">
+      <c r="R38" s="20" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>57.7</v>
+        <v>5.4</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="10" t="n">
-        <v>240.1</v>
-      </c>
-      <c r="W38" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.3</v>
+      <c r="V38" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="W38" s="20" t="n">
+        <v>12790.1</v>
+      </c>
+      <c r="X38" s="14" t="n">
+        <v>111.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3618,72 +3694,76 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E39" s="12" t="n">
+      <c r="C39" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>8</v>
+      <c r="G39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L39" s="12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L39" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>8.4</v>
+        <v>84.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="14" t="inlineStr"/>
-      <c r="S39" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q39" s="13" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="R39" s="13" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V39" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W39" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V39" s="13" t="n">
+        <v>75.42999999999999</v>
+      </c>
+      <c r="W39" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="14" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+        <v>64.8</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>48.8</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3697,65 +3777,65 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>22.8</v>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>22.5</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.4</v>
+        <v>16.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12" t="n">
+      <c r="J40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L40" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="M40" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N40" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="O40" s="12" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="P40" s="12" t="n">
-        <v>2.6</v>
+      <c r="M40" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="12" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="U40" s="14" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3779,25 +3859,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>22.1</v>
+        <v>11.1</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>2.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
+        <v>20.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3805,49 +3885,49 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>1.7</v>
+      <c r="M41" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W41" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3862,70 +3942,74 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
-        <v>30.4</v>
+      <c r="D42" s="13" t="n">
+        <v>48.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>14</v>
+      <c r="F42" s="14" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N42" s="3" t="n">
+      <c r="L42" s="11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R42" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="O42" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R42" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="n">
+      <c r="S42" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T42" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>57</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3942,17 +4026,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>174.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3963,17 +4049,17 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="L43" s="11" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="14" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
@@ -3982,31 +4068,31 @@
         <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="S43" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X43" s="12" t="n">
+      <c r="W43" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y43" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z43" s="12" t="n">
+      <c r="Y43" s="3" t="n">
         <v>14.8</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4022,51 +4108,51 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>98</v>
-      </c>
-      <c r="E44" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" s="13" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="9" t="n">
-        <v>21.7</v>
+      <c r="F44" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>14.2</v>
+        <v>26.1</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>15.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>1.5</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="L44" s="11" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
+        <v>154.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" s="14" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4075,12 +4161,14 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="n">
+      <c r="U44" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="3" t="n">
-        <v>30</v>
+      <c r="W44" s="11" t="n">
+        <v>20.6</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4088,7 +4176,9 @@
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4103,71 +4193,75 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>830.6</v>
+      <c r="D45" s="20" t="n">
+        <v>1165.8</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>135.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>22</v>
+        <v>53.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="K45" s="10" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="L45" s="10" t="n">
-        <v>1089.6</v>
-      </c>
-      <c r="M45" s="10" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="K45" s="20" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="M45" s="20" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O45" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>499</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="10" t="n">
-        <v>650.2</v>
-      </c>
-      <c r="R45" s="10" t="n">
-        <v>1.3</v>
+      <c r="Q45" s="20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="R45" s="20" t="n">
+        <v>1191.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>746.4</v>
+        <v>115.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>217.9</v>
+        <v>517.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="V45" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>114.8</v>
+        <v>187.1</v>
+      </c>
+      <c r="V45" s="20" t="n">
+        <v>1543</v>
+      </c>
+      <c r="W45" s="11" t="n">
+        <v>114.6</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.8</v>
+        <v>392.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>11141.1</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4182,17 +4276,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="9" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="20" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E46" s="20" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>22.8</v>
+      <c r="F46" s="20" t="n">
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4203,50 +4297,54 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M46" s="10" t="n">
+      <c r="K46" s="3" t="n">
+        <v>72162.8</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M46" s="20" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>17.2</v>
+      <c r="N46" s="14" t="n">
+        <v>54.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q46" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Q46" s="20" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="20" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>19.3</v>
+      <c r="S46" s="14" t="n">
+        <v>19.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="20" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>19.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -35,20 +35,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,16 +140,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,19 +161,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -796,17 +781,17 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="11" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F4" s="11" t="n">
+      <c r="D4" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>23</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
@@ -817,25 +802,25 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q4" s="13" t="n">
+      <c r="L4" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q4" s="14" t="n">
         <v>84</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -848,8 +833,8 @@
         <v>20.5</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr"/>
-      <c r="W4" s="11" t="inlineStr"/>
+      <c r="V4" s="10" t="inlineStr"/>
+      <c r="W4" s="10" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -867,18 +852,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D5" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -890,23 +875,23 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="L5" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M5" s="10" t="n">
         <v>15.8</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>3.4</v>
+      <c r="N5" s="10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
@@ -923,19 +908,19 @@
       <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="10" t="n">
         <v>15.7</v>
       </c>
-      <c r="X5" s="11" t="n">
+      <c r="X5" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y5" s="11" t="n">
+      <c r="Y5" s="10" t="n">
         <v>56.5</v>
       </c>
-      <c r="Z5" s="11" t="n">
+      <c r="Z5" s="10" t="n">
         <v>13.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -954,16 +939,16 @@
       <c r="C6" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -975,22 +960,22 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="O6" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="P6" s="10" t="n">
         <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
@@ -1003,24 +988,24 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="V6" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="X6" s="11" t="n">
+      <c r="X6" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y6" s="11" t="n">
+      <c r="Y6" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="Z6" s="11" t="n">
+      <c r="Z6" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1037,49 +1022,49 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D7" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>24.1</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="10" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="13" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="M7" s="14" t="n">
+      <c r="L7" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M7" s="10" t="n">
         <v>17.4</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="13" t="n">
-        <v>0.4</v>
+      <c r="N7" s="10" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
@@ -1088,25 +1073,25 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>656.4</v>
+        <v>56.4</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W7" s="11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X7" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Y7" s="11" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="Z7" s="11" t="n">
-        <v>10.4</v>
+      <c r="W7" s="10" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X7" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Y7" s="10" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="Z7" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1122,20 +1107,20 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>13.6</v>
+      <c r="D8" s="10" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>13.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6.9</v>
@@ -1143,23 +1128,23 @@
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>4</v>
+      <c r="L8" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>2.6</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
@@ -1176,19 +1161,19 @@
       <c r="U8" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="X8" s="11" t="n">
+      <c r="X8" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="Y8" s="11" t="n">
+      <c r="Y8" s="10" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="Z8" s="11" t="n">
+      <c r="Z8" s="10" t="n">
         <v>10.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1205,34 +1190,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>145.5</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>116.9</v>
+      <c r="F9" s="10" t="n">
+        <v>117.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K9" s="11" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" s="17" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1244,32 +1229,32 @@
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" s="20" t="n">
-        <v>142.8</v>
-      </c>
-      <c r="R9" s="20" t="n">
-        <v>1196</v>
+      <c r="Q9" s="17" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="R9" s="17" t="n">
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>182.6</v>
+        <v>122.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9255.1</v>
+        <v>255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="10" t="n">
         <v>101.4</v>
       </c>
-      <c r="W9" s="11" t="n">
-        <v>73.2</v>
+      <c r="W9" s="10" t="n">
+        <v>70.5</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>26.2</v>
+        <v>56.2</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>67</v>
@@ -1288,16 +1273,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>29.1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="10" t="n">
         <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1307,54 +1292,54 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="20" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q10" s="20" t="n">
+      <c r="N10" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" s="17" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="20" t="n">
+      <c r="R10" s="17" t="n">
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="X10" s="11" t="n">
+      <c r="X10" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="Y10" s="11" t="n">
+      <c r="Y10" s="10" t="n">
         <v>69.8</v>
       </c>
-      <c r="Z10" s="11" t="n">
+      <c r="Z10" s="10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1371,13 +1356,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1387,7 +1372,7 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1395,47 +1380,47 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+      <c r="M11" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q11" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>425.4</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="13" t="n">
+      <c r="S11" s="10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T11" s="10" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V11" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="W11" s="13" t="n">
+      <c r="W11" s="14" t="n">
         <v>19.51</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>48.9</v>
+        <v>58.9</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1454,16 +1439,16 @@
       <c r="C12" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1478,37 +1463,37 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="10" t="n">
         <v>17.4</v>
       </c>
-      <c r="N12" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q12" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R12" s="11" t="n">
+      <c r="N12" s="10" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R12" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V12" s="13" t="n">
+      <c r="S12" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V12" s="14" t="n">
         <v>45.4</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1537,16 +1522,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1561,35 +1546,35 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="L13" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" s="10" t="n">
         <v>15.8</v>
       </c>
-      <c r="N13" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+      <c r="N13" s="10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>14</v>
+      <c r="S13" s="10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>10.4</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>25.6</v>
@@ -1620,16 +1605,16 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1638,41 +1623,41 @@
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="14" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>714.5</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q14" s="3" t="n">
+      <c r="N14" s="10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="14" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>17</v>
+      <c r="S14" s="10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>12.7</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>23.6</v>
@@ -1703,16 +1688,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="11" t="n">
+      <c r="E15" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1727,35 +1712,35 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="10" t="n">
         <v>15.9</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>18.8</v>
+      <c r="S15" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="U15" s="10" t="n">
+        <v>14.4</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
@@ -1788,20 +1773,20 @@
       <c r="C16" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>138.8</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="17" t="n">
         <v>89</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="17" t="n">
         <v>113.9</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="10" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>288.2</v>
+        <v>81.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1809,32 +1794,32 @@
       <c r="J16" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="M16" s="11" t="n">
-        <v>84.09999999999999</v>
+      <c r="M16" s="17" t="n">
+        <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>909.4</v>
+        <v>904.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>40</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="Q16" s="20" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Q16" s="10" t="n">
         <v>138.2</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="10" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>66.8</v>
@@ -1842,20 +1827,20 @@
       <c r="U16" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="V16" s="20" t="n">
+      <c r="V16" s="17" t="n">
         <v>122.8</v>
       </c>
-      <c r="W16" s="20" t="n">
+      <c r="W16" s="17" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1871,16 +1856,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="10" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1893,50 +1878,50 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="14" t="n">
+      <c r="N17" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q17" s="20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R17" s="11" t="n">
+      <c r="O17" s="10" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V17" s="20" t="n">
+      <c r="S17" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="T17" s="10" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="V17" s="17" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="20" t="n">
-        <v>11</v>
+      <c r="W17" s="17" t="n">
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1068.5</v>
+        <v>22.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>810.8</v>
+        <v>254.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1954,13 +1939,13 @@
       <c r="C18" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="D18" s="10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F18" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1975,13 +1960,13 @@
       <c r="J18" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="13" t="n">
+      <c r="L18" s="14" t="n">
         <v>49.6</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1993,10 +1978,10 @@
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="13" t="n">
+      <c r="Q18" s="14" t="n">
         <v>90.47</v>
       </c>
-      <c r="R18" s="13" t="n">
+      <c r="R18" s="14" t="n">
         <v>44.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2008,20 +1993,20 @@
       <c r="U18" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V18" s="13" t="n">
+      <c r="V18" s="14" t="n">
         <v>46.47</v>
       </c>
-      <c r="W18" s="13" t="n">
+      <c r="W18" s="14" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>86</v>
+        <v>14.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.7</v>
+        <v>20.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2037,16 +2022,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="10" t="n">
         <v>29.6</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="10" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2058,41 +2043,41 @@
       <c r="J19" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N19" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="M19" s="10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="P19" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="10" t="n">
         <v>29.6</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="10" t="n">
         <v>46.8</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" s="10" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2101,7 +2086,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>294</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2122,20 +2107,20 @@
       <c r="C20" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="10" t="n">
         <v>12.4</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>87.40000000000001</v>
+      <c r="H20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>7.9</v>
@@ -2143,53 +2128,53 @@
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L20" s="3" t="n">
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="11" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" s="10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N20" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="O20" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="O20" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="P20" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="S20" s="11" t="n">
+      <c r="S20" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="10" t="n">
         <v>47.5</v>
       </c>
-      <c r="U20" s="11" t="n">
+      <c r="U20" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X20" s="3" t="n">
+      <c r="W20" s="10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X20" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="Y20" s="3" t="n">
+      <c r="Y20" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+      <c r="Z20" s="10" t="n">
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2205,16 +2190,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="10" t="n">
         <v>8.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2226,52 +2211,52 @@
       <c r="J21" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L21" s="3" t="n">
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="11" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N21" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="M21" s="10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="P21" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="Q21" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S21" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="T21" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V21" s="3" t="n">
+      <c r="T21" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X21" s="3" t="n">
+      <c r="W21" s="10" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X21" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="Y21" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Y21" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z21" s="10" t="n">
         <v>12.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2288,18 +2273,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2311,17 +2296,17 @@
       <c r="J22" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M22" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2329,19 +2314,19 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="10" t="n">
         <v>17.1</v>
       </c>
-      <c r="S22" s="11" t="n">
+      <c r="S22" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="T22" s="11" t="n">
+      <c r="T22" s="10" t="n">
         <v>68.3</v>
       </c>
-      <c r="U22" s="11" t="n">
+      <c r="U22" s="10" t="n">
         <v>9</v>
       </c>
       <c r="V22" s="3" t="n">
@@ -2354,10 +2339,10 @@
         <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>254.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2375,17 +2360,17 @@
       <c r="C23" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D23" s="10" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>117.5</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>36.2</v>
+      <c r="G23" s="10" t="n">
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
@@ -2396,13 +2381,13 @@
       <c r="J23" s="3" t="n">
         <v>52.9</v>
       </c>
-      <c r="K23" s="20" t="n">
+      <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="20" t="n">
-        <v>92</v>
-      </c>
-      <c r="M23" s="11" t="n">
+      <c r="L23" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="M23" s="17" t="n">
         <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2414,10 +2399,10 @@
       <c r="P23" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q23" s="20" t="n">
+      <c r="Q23" s="17" t="n">
         <v>140.4</v>
       </c>
-      <c r="R23" s="20" t="n">
+      <c r="R23" s="17" t="n">
         <v>103.4</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2427,13 +2412,13 @@
         <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="V23" s="20" t="n">
-        <v>1123.5</v>
-      </c>
-      <c r="W23" s="20" t="n">
-        <v>935.6</v>
+        <v>91.5</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="W23" s="17" t="n">
+        <v>95.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>26</v>
@@ -2442,7 +2427,7 @@
         <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>652.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2458,20 +2443,20 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="10" t="n">
         <v>29.1</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="10" t="n">
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2480,50 +2465,50 @@
         <v>10.6</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="20" t="n">
+      <c r="L24" s="17" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="17" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.4</v>
+        <v>25.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="20" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="R24" s="20" t="n">
+      <c r="Q24" s="17" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="R24" s="17" t="n">
         <v>20.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V24" s="20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W24" s="20" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="Y24" s="3" t="n">
-        <v>118.9</v>
+        <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2541,20 +2526,20 @@
       <c r="C25" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G25" s="11" t="n">
+      <c r="E25" s="10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2566,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>16.3</v>
@@ -2580,10 +2565,10 @@
       <c r="P25" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q25" s="13" t="n">
+      <c r="Q25" s="14" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2593,7 +2578,7 @@
         <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="W25" s="3" t="n">
@@ -2603,7 +2588,7 @@
         <v>9.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2622,49 +2607,49 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>16.8</v>
+      <c r="H26" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>8</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
+      <c r="M26" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O26" s="10" t="n">
         <v>86</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>5</v>
+      <c r="P26" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2676,20 +2661,20 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X26" s="3" t="n">
+      <c r="W26" s="10" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X26" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="Y26" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+      <c r="Y26" s="10" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="Z26" s="10" t="n">
+        <v>12.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2704,21 +2689,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
+      <c r="C27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>16.2</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
@@ -2727,40 +2714,40 @@
         <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="S27" s="11" t="n">
+      <c r="S27" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="T27" s="11" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U27" s="11" t="n">
+      <c r="T27" s="10" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="U27" s="10" t="n">
         <v>15.8</v>
       </c>
-      <c r="V27" s="13" t="n">
-        <v>64.8</v>
+      <c r="V27" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>19.8</v>
@@ -2790,74 +2777,74 @@
       <c r="C28" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G28" s="11" t="n">
+      <c r="E28" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G28" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>66</v>
+      <c r="H28" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="P28" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q28" s="10" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="R28" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="L28" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M28" s="11" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="N28" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O28" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="P28" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q28" s="11" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R28" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S28" s="11" t="n">
+      <c r="S28" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="T28" s="11" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="U28" s="11" t="n">
+      <c r="T28" s="10" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="U28" s="10" t="n">
         <v>15.8</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>29.6</v>
+      <c r="V28" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2875,68 +2862,68 @@
       <c r="C29" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="E29" s="10" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G29" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="M29" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N29" s="11" t="n">
+      <c r="N29" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="O29" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" s="10" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q29" s="11" t="n">
+      <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S29" s="11" t="n">
+      <c r="R29" s="10" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T29" s="11" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="U29" s="11" t="n">
+      <c r="T29" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="14" t="n">
-        <v>19</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2958,34 +2945,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="10" t="n">
         <v>133.2</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="17" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="17" t="n">
         <v>109.5</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="10" t="n">
         <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="K30" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="K30" s="17" t="n">
         <v>308.4</v>
       </c>
-      <c r="L30" s="20" t="n">
+      <c r="L30" s="17" t="n">
         <v>9434.799999999999</v>
       </c>
-      <c r="M30" s="20" t="n">
+      <c r="M30" s="17" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2997,10 +2984,10 @@
       <c r="P30" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q30" s="20" t="n">
+      <c r="Q30" s="17" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="20" t="n">
+      <c r="R30" s="17" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3010,19 +2997,19 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V30" s="20" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="W30" s="20" t="n">
-        <v>90.59999999999999</v>
+        <v>70.8</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="W30" s="17" t="n">
+        <v>9.5</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>916.2</v>
+        <v>336.2</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>47.6</v>
@@ -3043,20 +3030,20 @@
       <c r="C31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -3065,26 +3052,26 @@
         <v>6.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="20" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M31" s="20" t="n">
+      <c r="L31" s="17" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M31" s="17" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>205.1</v>
+        <v>5.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="20" t="n">
+      <c r="Q31" s="17" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="20" t="n">
-        <v>18.8</v>
+      <c r="R31" s="17" t="n">
+        <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3095,10 +3082,10 @@
       <c r="U31" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="V31" s="20" t="n">
+      <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="20" t="n">
+      <c r="W31" s="17" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3108,7 +3095,7 @@
         <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3124,16 +3111,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E32" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="E32" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G32" s="10" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3145,44 +3132,48 @@
       <c r="J32" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
-      <c r="O32" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="13" t="n">
+      <c r="Q32" s="14" t="n">
         <v>2.4</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>96.8</v>
+        <v>56.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>198.1</v>
       </c>
-      <c r="V32" s="11" t="inlineStr"/>
-      <c r="W32" s="13" t="n">
+      <c r="V32" s="10" t="inlineStr"/>
+      <c r="W32" s="14" t="n">
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>4412.8</v>
+        <v>912.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3201,16 +3192,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3220,55 +3211,55 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="M33" s="10" t="n">
         <v>14.7</v>
       </c>
-      <c r="N33" s="11" t="n">
+      <c r="N33" s="10" t="n">
         <v>16.7</v>
       </c>
-      <c r="O33" s="11" t="n">
+      <c r="O33" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P33" s="10" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V33" s="11" t="n">
+      <c r="R33" s="10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T33" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="U33" s="10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V33" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X33" s="3" t="n">
+      <c r="W33" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X33" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y33" s="3" t="n">
+      <c r="Y33" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="Z33" s="3" t="n">
-        <v>5.6</v>
+      <c r="Z33" s="10" t="n">
+        <v>6.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3284,16 +3275,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="13" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F34" s="3" t="n">
+      <c r="D34" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F34" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3305,53 +3296,53 @@
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L34" s="11" t="n">
+      <c r="K34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+      <c r="N34" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="P34" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q34" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S34" s="3" t="n">
+      <c r="R34" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="S34" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="10" t="n">
         <v>57.2</v>
       </c>
-      <c r="U34" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="V34" s="11" t="n">
+      <c r="U34" s="10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X34" s="3" t="n">
+      <c r="W34" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X34" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y34" s="3" t="n">
+      <c r="Y34" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+      <c r="Z34" s="10" t="n">
+        <v>10.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3367,74 +3358,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="E35" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="E35" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G35" s="10" t="n">
         <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N35" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+      <c r="O35" s="10" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S35" s="3" t="n">
+      <c r="R35" s="10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S35" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="T35" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="U35" s="3" t="n">
+      <c r="T35" s="10" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U35" s="10" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="11" t="n">
+      <c r="V35" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X35" s="3" t="n">
+      <c r="W35" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X35" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="Y35" s="3" t="n">
+      <c r="Y35" s="10" t="n">
         <v>86.5</v>
       </c>
-      <c r="Z35" s="3" t="n">
-        <v>0.3</v>
+      <c r="Z35" s="10" t="n">
+        <v>3.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3450,16 +3441,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3471,40 +3462,40 @@
       <c r="J36" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M36" s="11" t="n">
+      <c r="L36" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="10" t="n">
         <v>16.5</v>
       </c>
-      <c r="N36" s="11" t="n">
+      <c r="N36" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="P36" s="11" t="n">
+      <c r="P36" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="14" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S36" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="10" t="n">
         <v>56.4</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" s="11" t="n">
+      <c r="U36" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="V36" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3514,7 +3505,7 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3530,15 +3521,17 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="20" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>8821.799999999999</v>
-      </c>
-      <c r="F37" s="20" t="n">
-        <v>11</v>
+      <c r="C37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>111</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>45.6</v>
@@ -3552,32 +3545,32 @@
       <c r="J37" s="3" t="n">
         <v>31.5</v>
       </c>
-      <c r="K37" s="20" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="L37" s="11" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="M37" s="20" t="n">
-        <v>4.6</v>
+      <c r="K37" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>81</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20.8</v>
+        <v>30.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="Q37" s="20" t="n">
-        <v>131.8</v>
-      </c>
-      <c r="R37" s="20" t="n">
-        <v>1082.2</v>
+        <v>14.4</v>
+      </c>
+      <c r="Q37" s="17" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="R37" s="17" t="n">
+        <v>162.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1181.5</v>
+        <v>101.7</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3585,17 +3578,17 @@
       <c r="U37" s="3" t="n">
         <v>79.8</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="V37" s="10" t="n">
         <v>87.2</v>
       </c>
-      <c r="W37" s="20" t="n">
-        <v>998.1</v>
+      <c r="W37" s="17" t="n">
+        <v>250.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>101.4</v>
+        <v>14.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3614,72 +3607,72 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E38" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F38" s="20" t="n">
+      <c r="F38" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17</v>
+        <v>1.7</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M38" s="20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O38" s="3" t="n">
+      <c r="L38" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O38" s="10" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="P38" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="20" t="n">
+      <c r="Q38" s="17" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="20" t="n">
+      <c r="R38" s="17" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.4</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="W38" s="20" t="n">
-        <v>12790.1</v>
-      </c>
-      <c r="X38" s="14" t="n">
-        <v>111.9</v>
+      <c r="W38" s="17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3695,15 +3688,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="E39" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3716,50 +3709,50 @@
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L39" s="11" t="n">
+      <c r="K39" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L39" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q39" s="13" t="n">
+      <c r="Q39" s="10" t="n">
         <v>46.65</v>
       </c>
-      <c r="R39" s="13" t="n">
+      <c r="R39" s="10" t="n">
         <v>20.48</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="V39" s="13" t="n">
+      <c r="S39" s="10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T39" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="U39" s="10" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="V39" s="14" t="n">
         <v>75.42999999999999</v>
       </c>
-      <c r="W39" s="11" t="n">
+      <c r="W39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>48.8</v>
@@ -3778,17 +3771,17 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0.8</v>
+      <c r="D40" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>16.4</v>
@@ -3797,45 +3790,45 @@
         <v>2.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="L40" s="11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="M40" s="11" t="n">
+      <c r="M40" s="10" t="n">
         <v>16.5</v>
       </c>
-      <c r="N40" s="11" t="n">
+      <c r="N40" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="O40" s="11" t="n">
+      <c r="O40" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="P40" s="11" t="n">
+      <c r="P40" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="U40" s="14" t="n">
-        <v>94.40000000000001</v>
+      <c r="Q40" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="S40" s="10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T40" s="10" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="U40" s="10" t="n">
+        <v>10.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3859,16 +3852,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>20.1</v>
@@ -3882,50 +3875,50 @@
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>15.2</v>
+      <c r="M41" s="10" t="n">
+        <v>17.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q41" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
+      <c r="R41" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="S41" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="T41" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="U41" s="3" t="n">
+      <c r="T41" s="10" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W41" s="11" t="n">
+      <c r="V41" s="14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W41" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3942,74 +3935,74 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E42" s="3" t="n">
+      <c r="D42" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E42" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="14" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>94</v>
+      <c r="F42" s="10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L42" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="N42" s="11" t="n">
+      <c r="N42" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="O42" s="11" t="n">
+      <c r="O42" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="P42" s="11" t="n">
+      <c r="P42" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" s="11" t="n">
+      <c r="Q42" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="11" t="n">
+      <c r="R42" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="S42" s="11" t="n">
+      <c r="S42" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="T42" s="11" t="n">
+      <c r="T42" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="U42" s="11" t="n">
+      <c r="U42" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="11" t="n">
+      <c r="W42" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.4</v>
+        <v>57</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4025,20 +4018,20 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>174.4</v>
+      <c r="D43" s="10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -4046,43 +4039,43 @@
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L43" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="14" t="n">
+      <c r="M43" s="10" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="S43" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>25.9</v>
+      <c r="S43" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="T43" s="10" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="U43" s="10" t="n">
+        <v>-0.3</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4092,7 +4085,7 @@
         <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>21.9</v>
+        <v>57</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4110,65 +4103,65 @@
       <c r="C44" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="13" t="n">
+      <c r="D44" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E44" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="13" t="n">
-        <v>12</v>
+      <c r="F44" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>26.1</v>
+        <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K44" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K44" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
+      <c r="M44" s="10" t="n">
+        <v>15.6</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>154.8</v>
+        <v>82</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R44" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="S44" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>2.3</v>
+      <c r="S44" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T44" s="10" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="U44" s="10" t="n">
+        <v>-1.9</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="11" t="n">
-        <v>20.6</v>
+      <c r="W44" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4177,7 +4170,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>21</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4192,75 +4185,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="20" t="n">
-        <v>1165.8</v>
-      </c>
-      <c r="E45" s="20" t="n">
+      <c r="C45" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>102.8</v>
       </c>
-      <c r="F45" s="20" t="n">
-        <v>135.9</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="F45" s="17" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="G45" s="10" t="n">
         <v>65</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>53.5</v>
+        <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.3</v>
       </c>
-      <c r="K45" s="20" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="L45" s="11" t="n">
+      <c r="K45" s="10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L45" s="10" t="n">
         <v>110.7</v>
       </c>
-      <c r="M45" s="20" t="n">
+      <c r="M45" s="17" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>499</v>
+        <v>99</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="R45" s="20" t="n">
-        <v>1191.1</v>
+      <c r="Q45" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>115.8</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>115.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>517.9</v>
+        <v>17.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>187.1</v>
-      </c>
-      <c r="V45" s="20" t="n">
-        <v>1543</v>
-      </c>
-      <c r="W45" s="11" t="n">
-        <v>114.6</v>
+        <v>107.1</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>143</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>114</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>392.9</v>
+        <v>93.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11141.1</v>
+        <v>114</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4276,17 +4271,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="17" t="n">
         <v>27.9</v>
       </c>
-      <c r="E46" s="20" t="n">
+      <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="20" t="n">
+      <c r="F46" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>19.8</v>
+      <c r="G46" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4298,42 +4293,42 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>72162.8</v>
-      </c>
-      <c r="L46" s="11" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M46" s="20" t="n">
+      <c r="M46" s="17" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="14" t="n">
-        <v>54.9</v>
+      <c r="N46" s="3" t="n">
+        <v>51.1</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="Q46" s="20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q46" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="20" t="n">
+      <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="14" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V46" s="20" t="n">
+      <c r="S46" s="10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="T46" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="U46" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V46" s="17" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="10" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
@@ -4343,7 +4338,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>28.6</v>
@@ -988,7 +988,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58.3</v>
+        <v>56.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1123,7 +1123,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1303,14 +1303,14 @@
       <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
-      <c r="N10" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="P10" s="10" t="n">
-        <v>2.1</v>
+      <c r="N10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>3.2</v>
       </c>
       <c r="Q10" s="17" t="n">
         <v>29.2</v>
@@ -1377,7 +1377,7 @@
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>28.2</v>
@@ -1460,7 +1460,7 @@
       <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -1543,8 +1543,8 @@
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="10" t="n">
         <v>17.6</v>
@@ -1626,7 +1626,7 @@
       <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -1692,10 +1692,10 @@
         <v>28.8</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1709,7 +1709,7 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -1786,7 +1786,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>84.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1837,7 +1837,7 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>61</v>
@@ -1915,13 +1915,13 @@
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.2</v>
+        <v>120.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>254.1</v>
+        <v>902.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>30.4</v>
@@ -2000,10 +2000,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>58</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="10" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>17.8</v>
@@ -2086,7 +2086,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>54</v>
+        <v>28.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>30.6</v>
@@ -2230,7 +2230,7 @@
         <v>2.8</v>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>17.1</v>
@@ -2342,7 +2342,7 @@
         <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>145.6</v>
@@ -2490,19 +2490,19 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>2.2</v>
+        <v>13.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="17" t="n">
-        <v>11.7</v>
+        <v>24.7</v>
       </c>
       <c r="W24" s="17" t="n">
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>18.4</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>22.8</v>
@@ -2539,7 +2539,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2620,7 +2620,7 @@
         <v>11.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
@@ -2696,12 +2696,12 @@
         <v>27.4</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G27" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G27" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>27.4</v>
@@ -2790,13 +2790,13 @@
         <v>9.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
@@ -3003,7 +3003,7 @@
         <v>118.2</v>
       </c>
       <c r="W30" s="17" t="n">
-        <v>9.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>26.6</v>
@@ -3053,16 +3053,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="17" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="M31" s="17" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
+        <v>25.6</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3077,10 +3077,10 @@
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>59.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>23.6</v>
@@ -3092,7 +3092,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>18</v>
@@ -3130,7 +3130,7 @@
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>7.2</v>
@@ -3170,10 +3170,10 @@
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>912.2</v>
+        <v>9119.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>1.5</v>
+        <v>26.2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3231,19 +3231,19 @@
       <c r="P33" s="10" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R33" s="10" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S33" s="10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T33" s="10" t="n">
+      <c r="R33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T33" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="U33" s="10" t="n">
+      <c r="U33" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V33" s="10" t="n">
@@ -3357,7 +3357,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
@@ -3374,7 +3376,7 @@
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3522,7 +3524,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>133.8</v>
@@ -3567,10 +3569,10 @@
         <v>133.8</v>
       </c>
       <c r="R37" s="17" t="n">
-        <v>162.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
+        <v>218.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3582,10 +3584,10 @@
         <v>87.2</v>
       </c>
       <c r="W37" s="17" t="n">
-        <v>250.1</v>
+        <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>14.3</v>
+        <v>1014.3</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>86</v>
@@ -3620,7 +3622,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>1.7</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.2</v>
@@ -3633,16 +3635,16 @@
         <v>18.1</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>86.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="P38" s="10" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="17" t="n">
         <v>26.8</v>
@@ -3666,13 +3668,13 @@
         <v>11.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>88.8</v>
+        <v>21.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3718,29 +3720,29 @@
       <c r="M39" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q39" s="10" t="n">
+      <c r="N39" s="10" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O39" s="10" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="P39" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q39" s="14" t="n">
         <v>46.65</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>20.48</v>
       </c>
-      <c r="S39" s="10" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="T39" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="U39" s="10" t="n">
-        <v>80.59999999999999</v>
+      <c r="S39" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="V39" s="14" t="n">
         <v>75.42999999999999</v>
@@ -3772,13 +3774,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="10" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>7.8</v>
@@ -3810,20 +3812,20 @@
       <c r="P40" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="S40" s="10" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="T40" s="10" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="U40" s="10" t="n">
-        <v>10.6</v>
+      <c r="S40" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
@@ -3852,7 +3854,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>25.4</v>
@@ -3870,7 +3872,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3884,14 +3886,14 @@
       <c r="M41" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>4.2</v>
+      <c r="N41" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O41" s="10" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="P41" s="10" t="n">
+        <v>2.9</v>
       </c>
       <c r="Q41" s="10" t="n">
         <v>22.6</v>
@@ -3903,13 +3905,13 @@
         <v>17.2</v>
       </c>
       <c r="T41" s="10" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="V41" s="14" t="n">
-        <v>1.9</v>
+      <c r="V41" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W41" s="10" t="n">
         <v>16.8</v>
@@ -3918,7 +3920,7 @@
         <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3936,15 +3938,15 @@
       </c>
       <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="10" t="n">
-        <v>29</v>
+        <v>28.4</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>16</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G42" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G42" s="10" t="n">
         <v>12.6</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3960,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="M42" s="10" t="n">
         <v>15</v>
@@ -4019,10 +4021,10 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="10" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>22.7</v>
@@ -4048,29 +4050,29 @@
       <c r="M43" s="10" t="n">
         <v>14.8</v>
       </c>
-      <c r="N43" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>3</v>
+      <c r="N43" s="10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O43" s="10" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="P43" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="Q43" s="10" t="n">
-        <v>20.4</v>
+        <v>30.4</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>20.6</v>
+        <v>16.3</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>24.3</v>
+        <v>18.5</v>
       </c>
       <c r="T43" s="10" t="n">
-        <v>101.2</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="10" t="n">
-        <v>-0.3</v>
+        <v>25</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
@@ -4101,25 +4103,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>27.6</v>
+        <v>33.6</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>15.3</v>
@@ -4133,29 +4135,29 @@
       <c r="M44" s="10" t="n">
         <v>15.6</v>
       </c>
-      <c r="N44" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="P44" s="3" t="n">
+      <c r="N44" s="10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="O44" s="10" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="P44" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q44" s="10" t="n">
-        <v>20.6</v>
+      <c r="Q44" s="3" t="n">
+        <v>30.6</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="S44" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T44" s="10" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="U44" s="10" t="n">
-        <v>-1.9</v>
+      <c r="S44" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
@@ -4186,7 +4188,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D45" s="17" t="n">
         <v>167.8</v>
@@ -4207,37 +4209,37 @@
         <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>110.7</v>
+        <v>110.6</v>
       </c>
       <c r="M45" s="17" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>99</v>
+        <v>499</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="10" t="n">
-        <v>165</v>
+      <c r="Q45" s="17" t="n">
+        <v>16.5</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>115.8</v>
+        <v>111.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
@@ -4249,7 +4251,7 @@
         <v>114</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>93.5</v>
+        <v>393.6</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4293,37 +4295,37 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>51.8</v>
+        <v>280.8</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="M46" s="17" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q46" s="10" t="n">
+      <c r="N46" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O46" s="10" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q46" s="17" t="n">
         <v>27.5</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="T46" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="U46" s="10" t="n">
-        <v>13.2</v>
+      <c r="S46" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="V46" s="17" t="n">
         <v>23.8</v>
@@ -4338,7 +4340,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>28.6</v>
@@ -988,7 +988,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>56.3</v>
+        <v>58.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1123,7 +1123,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1236,7 +1236,7 @@
         <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>255.1</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>28.2</v>
@@ -1692,10 +1692,10 @@
         <v>28.8</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>138.8</v>
@@ -1786,7 +1786,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>84.2</v>
+        <v>89.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1882,16 +1882,16 @@
         <v>18.6</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>16.8</v>
+        <v>15.9</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>19.1</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>89.3</v>
+        <v>84</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" s="10" t="n">
         <v>27.6</v>
@@ -1915,13 +1915,13 @@
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>10.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>120.1</v>
+        <v>22</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>902.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>30.4</v>
@@ -2000,10 +2000,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.2</v>
+        <v>28.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>58</v>
@@ -2086,7 +2086,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>28.2</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2342,7 +2342,7 @@
         <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>145.6</v>
@@ -2472,10 +2472,10 @@
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>25.4</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
@@ -2490,7 +2490,7 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
@@ -2502,13 +2502,13 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>22.8</v>
@@ -2539,7 +2539,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>27.4</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>27.4</v>
@@ -2796,7 +2796,7 @@
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>13.2</v>
@@ -2958,7 +2958,7 @@
         <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>22</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>26.6</v>
@@ -3077,10 +3077,10 @@
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>23.6</v>
@@ -3092,7 +3092,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.2</v>
+        <v>57.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>18</v>
@@ -3170,10 +3170,10 @@
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>9119.1</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>26.2</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3231,19 +3231,19 @@
       <c r="P33" s="10" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T33" s="3" t="n">
+      <c r="R33" s="10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T33" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="10" t="n">
         <v>15.3</v>
       </c>
       <c r="V33" s="10" t="n">
@@ -3357,9 +3357,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
@@ -3572,7 +3570,7 @@
         <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>218.8</v>
+        <v>101.7</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3587,7 +3585,7 @@
         <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1014.3</v>
+        <v>1.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>86</v>
@@ -3635,16 +3633,16 @@
         <v>18.1</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>16.5</v>
+        <v>15.8</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>18.8</v>
+        <v>17.9</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>90.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="P38" s="10" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="Q38" s="17" t="n">
         <v>26.8</v>
@@ -3656,7 +3654,7 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
@@ -3665,13 +3663,13 @@
         <v>22</v>
       </c>
       <c r="W38" s="17" t="n">
-        <v>11.1</v>
+        <v>5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>21.8</v>
@@ -3747,7 +3745,7 @@
       <c r="V39" s="14" t="n">
         <v>75.42999999999999</v>
       </c>
-      <c r="W39" s="10" t="n">
+      <c r="W39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3774,10 +3772,10 @@
       </c>
       <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="10" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>22.3</v>
@@ -3812,25 +3810,25 @@
       <c r="P40" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="10" t="n">
         <v>26.2</v>
       </c>
       <c r="R40" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="S40" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S40" s="10" t="n">
         <v>19.7</v>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="T40" s="10" t="n">
         <v>57.8</v>
       </c>
-      <c r="U40" s="3" t="n">
-        <v>19.4</v>
+      <c r="U40" s="10" t="n">
+        <v>14.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3854,7 +3852,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>25.4</v>
@@ -3872,7 +3870,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3895,32 +3893,32 @@
       <c r="P41" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="S41" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="T41" s="10" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U41" s="10" t="n">
+      <c r="T41" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3994,7 +3992,7 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4077,8 +4075,8 @@
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="10" t="n">
-        <v>20</v>
+      <c r="W43" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>19.6</v>
@@ -4103,7 +4101,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>33.6</v>
@@ -4118,7 +4116,7 @@
         <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>15.2</v>
+        <v>18.8</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>7.6</v>
@@ -4162,7 +4160,7 @@
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
@@ -4172,7 +4170,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4188,12 +4186,12 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="17" t="n">
         <v>167.8</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="17" t="n">
         <v>102.8</v>
       </c>
       <c r="F45" s="17" t="n">
@@ -4209,7 +4207,7 @@
         <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.2</v>
+        <v>61.5</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>9.4</v>
@@ -4221,7 +4219,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>499</v>
@@ -4233,7 +4231,7 @@
         <v>16.5</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>111.5</v>
+        <v>111.3</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>116.2</v>
@@ -4247,8 +4245,8 @@
       <c r="V45" s="17" t="n">
         <v>143</v>
       </c>
-      <c r="W45" s="10" t="n">
-        <v>114</v>
+      <c r="W45" s="17" t="n">
+        <v>115.8</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>393.6</v>
@@ -4295,7 +4293,7 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>280.8</v>
+        <v>20.8</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>18.3</v>
@@ -4330,7 +4328,7 @@
       <c r="V46" s="17" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="17" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -812,13 +812,13 @@
         <v>16.8</v>
       </c>
       <c r="N4" s="10" t="n">
-        <v>19.1</v>
+        <v>17.9</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>89.3</v>
+        <v>83.5</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" s="14" t="n">
         <v>84</v>
@@ -885,13 +885,13 @@
         <v>15.8</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>89.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
@@ -912,7 +912,7 @@
         <v>24.8</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>15.7</v>
+        <v>18.6</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>17.8</v>
@@ -967,7 +967,7 @@
         <v>18.4</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>18.2</v>
@@ -997,7 +997,7 @@
         <v>24.6</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>20.7</v>
@@ -1055,13 +1055,13 @@
         <v>17.4</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>92.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>30.4</v>
@@ -1082,7 +1082,7 @@
         <v>25.8</v>
       </c>
       <c r="W7" s="10" t="n">
-        <v>16.9</v>
+        <v>19.6</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>19.2</v>
@@ -1138,13 +1138,13 @@
         <v>16.4</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>18.6</v>
+        <v>17.2</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>87.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
@@ -1168,13 +1168,13 @@
         <v>19.8</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>23.1</v>
+        <v>18.7</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>67.90000000000001</v>
+        <v>55</v>
       </c>
       <c r="Z8" s="10" t="n">
-        <v>10.9</v>
+        <v>15.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
       <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="10" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1248,7 +1248,7 @@
         <v>101.4</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>70.5</v>
+        <v>78</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>95.7</v>
@@ -1334,13 +1334,13 @@
         <v>19.5</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>22.7</v>
+        <v>18.6</v>
       </c>
       <c r="Y10" s="10" t="n">
-        <v>69.8</v>
+        <v>57.4</v>
       </c>
       <c r="Z10" s="10" t="n">
-        <v>9.800000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>17.2</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>92.7</v>
+        <v>88.8</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" s="10" t="n">
         <v>28.4</v>
@@ -1402,13 +1402,13 @@
         <v>20</v>
       </c>
       <c r="S11" s="10" t="n">
-        <v>23.4</v>
+        <v>17.6</v>
       </c>
       <c r="T11" s="10" t="n">
-        <v>60.4</v>
+        <v>45.5</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>15.3</v>
+        <v>21.1</v>
       </c>
       <c r="V11" s="14" t="n">
         <v>45.4</v>
@@ -1470,13 +1470,13 @@
         <v>17.4</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>92.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" s="10" t="n">
         <v>28.2</v>
@@ -1485,13 +1485,13 @@
         <v>21.6</v>
       </c>
       <c r="S12" s="10" t="n">
-        <v>25.8</v>
+        <v>21.3</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>67.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="V12" s="14" t="n">
         <v>45.4</v>
@@ -1553,13 +1553,13 @@
         <v>15.8</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>89.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="10" t="n">
         <v>26</v>
@@ -1568,13 +1568,13 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>23.2</v>
+        <v>19.1</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>69.09999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>25.6</v>
@@ -1636,13 +1636,13 @@
         <v>16.8</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>82.8</v>
+        <v>74</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="10" t="n">
         <v>26.8</v>
@@ -1651,13 +1651,13 @@
         <v>19.4</v>
       </c>
       <c r="S14" s="10" t="n">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="T14" s="10" t="n">
-        <v>63.9</v>
+        <v>49.5</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>12.7</v>
+        <v>17.8</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>23.6</v>
@@ -1716,7 +1716,7 @@
         <v>18.6</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>15.9</v>
+        <v>16.8</v>
       </c>
       <c r="N15" s="10" t="n">
         <v>18.1</v>
@@ -1734,13 +1734,13 @@
         <v>21.2</v>
       </c>
       <c r="S15" s="10" t="n">
-        <v>25.2</v>
+        <v>20</v>
       </c>
       <c r="T15" s="10" t="n">
-        <v>63.5</v>
+        <v>50.4</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>14.4</v>
+        <v>19.7</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
@@ -1800,7 +1800,7 @@
       <c r="L16" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1882,7 +1882,7 @@
         <v>18.6</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>15.9</v>
+        <v>16.8</v>
       </c>
       <c r="N17" s="10" t="n">
         <v>18.1</v>
@@ -1900,13 +1900,13 @@
         <v>20.4</v>
       </c>
       <c r="S17" s="10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="T17" s="10" t="n">
-        <v>64.90000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>13</v>
+        <v>17.9</v>
       </c>
       <c r="V17" s="17" t="n">
         <v>24.6</v>
@@ -2050,7 +2050,7 @@
         <v>18.6</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="N19" s="10" t="n">
         <v>18.7</v>
@@ -2064,8 +2064,8 @@
       <c r="Q19" s="10" t="n">
         <v>29.6</v>
       </c>
-      <c r="R19" s="10" t="n">
-        <v>17</v>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="S19" s="10" t="n">
         <v>19.4</v>
@@ -2135,7 +2135,7 @@
         <v>18.8</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="N20" s="10" t="n">
         <v>19</v>
@@ -2149,8 +2149,8 @@
       <c r="Q20" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="R20" s="10" t="n">
-        <v>18.2</v>
+      <c r="R20" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="S20" s="10" t="n">
         <v>20.9</v>
@@ -2164,8 +2164,8 @@
       <c r="V20" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="10" t="n">
-        <v>17.5</v>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>20</v>
@@ -2218,7 +2218,7 @@
         <v>18.8</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="N21" s="10" t="n">
         <v>19</v>
@@ -2232,8 +2232,8 @@
       <c r="Q21" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>17.1</v>
+      <c r="R21" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="S21" s="10" t="n">
         <v>19.5</v>
@@ -2247,8 +2247,8 @@
       <c r="V21" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="10" t="n">
-        <v>15.9</v>
+      <c r="W21" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>18</v>
@@ -2299,26 +2299,26 @@
       <c r="K22" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="10" t="n">
         <v>18.2</v>
       </c>
       <c r="M22" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="Q22" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="R22" s="10" t="n">
-        <v>17.1</v>
+      <c r="R22" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="S22" s="10" t="n">
         <v>19.5</v>
@@ -2387,7 +2387,7 @@
       <c r="L23" s="17" t="n">
         <v>93</v>
       </c>
-      <c r="M23" s="17" t="n">
+      <c r="M23" s="10" t="n">
         <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2468,7 +2468,7 @@
       <c r="L24" s="17" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="17" t="n">
+      <c r="M24" s="10" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2635,7 +2635,7 @@
         <v>18.4</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="N26" s="10" t="n">
         <v>18.2</v>
@@ -2664,8 +2664,8 @@
       <c r="V26" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W26" s="10" t="n">
-        <v>15.9</v>
+      <c r="W26" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>18</v>
@@ -2716,26 +2716,26 @@
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="M27" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="P27" s="3" t="n">
+      <c r="O27" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="P27" s="10" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="10" t="n">
         <v>27.4</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="S27" s="10" t="n">
         <v>20.7</v>
@@ -2805,7 +2805,7 @@
         <v>18.4</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
       <c r="N28" s="10" t="n">
         <v>17.8</v>
@@ -2820,7 +2820,7 @@
         <v>27.4</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="S28" s="10" t="n">
         <v>20.7</v>
@@ -2890,7 +2890,7 @@
         <v>18.6</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="N29" s="10" t="n">
         <v>19.1</v>
@@ -2972,7 +2972,7 @@
       <c r="L30" s="17" t="n">
         <v>9434.799999999999</v>
       </c>
-      <c r="M30" s="17" t="n">
+      <c r="M30" s="10" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2987,7 +2987,7 @@
       <c r="Q30" s="17" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="17" t="n">
+      <c r="R30" s="10" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3055,7 +3055,7 @@
       <c r="L31" s="17" t="n">
         <v>10.3</v>
       </c>
-      <c r="M31" s="17" t="n">
+      <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3070,7 +3070,7 @@
       <c r="Q31" s="17" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="17" t="n">
+      <c r="R31" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3142,13 +3142,13 @@
         <v>16.8</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>90.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="P32" s="10" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="Q32" s="14" t="n">
         <v>2.4</v>
@@ -3220,7 +3220,7 @@
         <v>17.4</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>14.7</v>
+        <v>15.6</v>
       </c>
       <c r="N33" s="10" t="n">
         <v>16.7</v>
@@ -3234,8 +3234,8 @@
       <c r="Q33" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R33" s="10" t="n">
-        <v>17.1</v>
+      <c r="R33" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="S33" s="10" t="n">
         <v>19.5</v>
@@ -3249,8 +3249,8 @@
       <c r="V33" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="10" t="n">
-        <v>17.2</v>
+      <c r="W33" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>19.6</v>
@@ -3306,19 +3306,19 @@
         <v>17.2</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="O34" s="10" t="n">
-        <v>92.7</v>
+        <v>88.8</v>
       </c>
       <c r="P34" s="10" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="10" t="n">
-        <v>19</v>
+      <c r="R34" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="S34" s="10" t="n">
         <v>21.9</v>
@@ -3332,8 +3332,8 @@
       <c r="V34" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="10" t="n">
-        <v>18.1</v>
+      <c r="W34" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>20.7</v>
@@ -3389,19 +3389,19 @@
         <v>15.8</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>89.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="P35" s="10" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="R35" s="10" t="n">
-        <v>16.6</v>
+      <c r="R35" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="S35" s="10" t="n">
         <v>18.9</v>
@@ -3416,13 +3416,13 @@
         <v>20.4</v>
       </c>
       <c r="W35" s="10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="Y35" s="10" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>3.2</v>
@@ -3469,7 +3469,7 @@
         <v>18.6</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="N36" s="10" t="n">
         <v>18.8</v>
@@ -3483,8 +3483,8 @@
       <c r="Q36" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="10" t="n">
-        <v>19.1</v>
+      <c r="R36" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="S36" s="10" t="n">
         <v>22.1</v>
@@ -3552,7 +3552,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>81</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>0.9</v>
@@ -3633,7 +3633,7 @@
         <v>18.1</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="N38" s="10" t="n">
         <v>17.9</v>
@@ -3719,13 +3719,13 @@
         <v>17.6</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>20.1</v>
+        <v>18.9</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>89.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P39" s="10" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q39" s="14" t="n">
         <v>46.65</v>
@@ -3799,7 +3799,7 @@
         <v>19.2</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="N40" s="10" t="n">
         <v>18.8</v>
@@ -3814,7 +3814,7 @@
         <v>26.2</v>
       </c>
       <c r="R40" s="10" t="n">
-        <v>17.3</v>
+        <v>20</v>
       </c>
       <c r="S40" s="10" t="n">
         <v>19.7</v>
@@ -3885,13 +3885,13 @@
         <v>17.2</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>87.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="P41" s="10" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
@@ -3963,7 +3963,7 @@
         <v>17.4</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="N42" s="10" t="n">
         <v>17</v>
@@ -3978,7 +3978,7 @@
         <v>28.6</v>
       </c>
       <c r="R42" s="10" t="n">
-        <v>17.8</v>
+        <v>21</v>
       </c>
       <c r="S42" s="10" t="n">
         <v>20.4</v>
@@ -4049,19 +4049,19 @@
         <v>14.8</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="O43" s="10" t="n">
-        <v>90.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P43" s="10" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q43" s="10" t="n">
         <v>30.4</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>16.3</v>
+        <v>20.6</v>
       </c>
       <c r="S43" s="10" t="n">
         <v>18.5</v>
@@ -4134,13 +4134,13 @@
         <v>15.6</v>
       </c>
       <c r="N44" s="10" t="n">
-        <v>17.7</v>
+        <v>15.5</v>
       </c>
       <c r="O44" s="10" t="n">
-        <v>81.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P44" s="10" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -4215,7 +4215,7 @@
       <c r="L45" s="10" t="n">
         <v>110.6</v>
       </c>
-      <c r="M45" s="17" t="n">
+      <c r="M45" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4231,7 +4231,7 @@
         <v>16.5</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>111.3</v>
+        <v>121.5</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>116.2</v>
@@ -4298,17 +4298,17 @@
       <c r="L46" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="17" t="n">
+      <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="O46" s="10" t="n">
-        <v>88.7</v>
+        <v>82.5</v>
       </c>
       <c r="P46" s="10" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q46" s="17" t="n">
         <v>27.5</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/904/904_197208_SF.JPG_post_QA_QC.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -174,12 +174,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1222,7 +1216,7 @@
       <c r="J9" s="3" t="n">
         <v>256.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1797,7 +1791,7 @@
       <c r="J16" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2353,13 +2347,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="18" t="n">
         <v>145.6</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="18" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="18" t="n">
         <v>110.8</v>
       </c>
       <c r="G23" s="15" t="n">
@@ -2374,7 +2368,7 @@
       <c r="J23" s="3" t="n">
         <v>52.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="18" t="n">
         <v>16.8</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2436,13 +2430,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="18" t="n">
         <v>29.1</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="18" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="18" t="n">
         <v>23.5</v>
       </c>
       <c r="G24" s="13" t="n">
@@ -2702,7 +2696,7 @@
       <c r="J27" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="14" t="n"/>
       <c r="L27" s="3" t="n">
         <v>98.8</v>
       </c>
@@ -2926,13 +2920,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="18" t="n">
         <v>133.4</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="18" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="20" t="n">
+      <c r="F30" s="18" t="n">
         <v>22.1</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2947,7 +2941,7 @@
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="18" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3007,13 +3001,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="18" t="n">
         <v>26.6</v>
       </c>
-      <c r="E31" s="20" t="n">
+      <c r="E31" s="18" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="20" t="n">
+      <c r="F31" s="18" t="n">
         <v>21.9</v>
       </c>
       <c r="G31" s="13" t="n">
@@ -3518,7 +3512,7 @@
       <c r="J37" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4141,13 +4135,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
-      <c r="D45" s="20" t="n">
+      <c r="D45" s="18" t="n">
         <v>24.8</v>
       </c>
-      <c r="E45" s="20" t="n">
+      <c r="E45" s="18" t="n">
         <v>17.1</v>
       </c>
-      <c r="F45" s="20" t="n">
+      <c r="F45" s="18" t="n">
         <v>22.5</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4162,7 +4156,7 @@
       <c r="J45" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="18" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
@@ -4224,13 +4218,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="18" t="n">
         <v>27.9</v>
       </c>
-      <c r="E46" s="20" t="n">
+      <c r="E46" s="18" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="20" t="n">
+      <c r="F46" s="18" t="n">
         <v>22.5</v>
       </c>
       <c r="G46" s="13" t="n">
